--- a/database/event/4411/event_4411_evp_summary.xlsx
+++ b/database/event/4411/event_4411_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.647399999999999</v>
+        <v>9.768599999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.714</v>
+        <v>2.7481</v>
       </c>
       <c r="D2" t="n">
-        <v>3.476</v>
+        <v>3.4479</v>
       </c>
       <c r="E2" t="n">
-        <v>9.647399999999999</v>
+        <v>9.768599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4343</v>
+        <v>3.5555</v>
       </c>
       <c r="G2" t="n">
         <v>6.2131</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4343</v>
+        <v>3.5555</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7836</v>
+        <v>2.8818</v>
       </c>
       <c r="J2" t="n">
         <v>6.2131</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>8.996700000000001</v>
+        <v>9.094899999999999</v>
       </c>
       <c r="N2" t="n">
         <v>259</v>
@@ -548,7 +548,7 @@
         <v>1.6715</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9789</v>
+        <v>1.9232</v>
       </c>
       <c r="E3" t="n">
         <v>5.9416</v>
@@ -594,7 +594,7 @@
         <v>1.1517</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2325</v>
+        <v>1.1871</v>
       </c>
       <c r="E4" t="n">
         <v>4.0939</v>
@@ -640,7 +640,7 @@
         <v>1.0537</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0917</v>
+        <v>1.0483</v>
       </c>
       <c r="E5" t="n">
         <v>3.7455</v>
@@ -686,7 +686,7 @@
         <v>1.0479</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0834</v>
+        <v>1.0401</v>
       </c>
       <c r="E6" t="n">
         <v>3.7249</v>
@@ -732,7 +732,7 @@
         <v>0.9376</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9251</v>
+        <v>0.8839</v>
       </c>
       <c r="E7" t="n">
         <v>3.3329</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8459</v>
+        <v>2.967</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8006</v>
+        <v>0.8347</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7381</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8459</v>
+        <v>2.967</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8929</v>
+        <v>3.014</v>
       </c>
       <c r="G8" t="n">
         <v>-0.047</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8929</v>
+        <v>3.014</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3448</v>
+        <v>2.443</v>
       </c>
       <c r="J8" t="n">
         <v>-0.047</v>
@@ -805,7 +805,7 @@
         <v>57</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2978</v>
+        <v>2.396</v>
       </c>
       <c r="N8" t="n">
         <v>138</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5714</v>
+        <v>2.7051</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7234</v>
+        <v>0.761</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6338</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5714</v>
+        <v>2.7051</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8035</v>
+        <v>2.9372</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2321</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8035</v>
+        <v>2.9372</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2723</v>
+        <v>2.3807</v>
       </c>
       <c r="J9" t="n">
         <v>-0.2321</v>
@@ -851,7 +851,7 @@
         <v>57</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0402</v>
+        <v>2.1486</v>
       </c>
       <c r="N9" t="n">
         <v>138</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0869</v>
+        <v>2.1418</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5871</v>
+        <v>0.6025</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4217</v>
+        <v>0.4094</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0869</v>
+        <v>2.1418</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0869</v>
+        <v>2.1418</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0869</v>
+        <v>2.1418</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0869</v>
+        <v>2.1418</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0869</v>
+        <v>2.1418</v>
       </c>
       <c r="N10" t="n">
         <v>153</v>
@@ -916,7 +916,7 @@
         <v>0.5725</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4007</v>
+        <v>0.3668</v>
       </c>
       <c r="E11" t="n">
         <v>2.0349</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9778</v>
+        <v>2.0201</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5564</v>
+        <v>0.5683</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3776</v>
+        <v>0.3609</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9778</v>
+        <v>2.0201</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0766</v>
+        <v>1.1189</v>
       </c>
       <c r="G12" t="n">
         <v>0.9012</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0766</v>
+        <v>1.1189</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8726</v>
+        <v>0.9069</v>
       </c>
       <c r="J12" t="n">
         <v>0.9012</v>
@@ -989,7 +989,7 @@
         <v>69</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7738</v>
+        <v>1.8081</v>
       </c>
       <c r="N12" t="n">
         <v>196</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7489</v>
+        <v>1.9823</v>
       </c>
       <c r="C13" t="n">
-        <v>0.492</v>
+        <v>0.5577</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2852</v>
+        <v>0.3458</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7489</v>
+        <v>1.9823</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7489</v>
+        <v>1.4313</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.551</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7489</v>
+        <v>1.4313</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7489</v>
+        <v>1.1601</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.551</v>
       </c>
       <c r="K13" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7489</v>
+        <v>1.7111</v>
       </c>
       <c r="N13" t="n">
-        <v>153</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7239</v>
+        <v>1.7489</v>
       </c>
       <c r="C14" t="n">
-        <v>0.485</v>
+        <v>0.492</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2751</v>
+        <v>0.2529</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7239</v>
+        <v>1.7489</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1729</v>
+        <v>1.7489</v>
       </c>
       <c r="G14" t="n">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1729</v>
+        <v>1.7489</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9507</v>
+        <v>1.7489</v>
       </c>
       <c r="J14" t="n">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L14" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5017</v>
+        <v>1.7489</v>
       </c>
       <c r="N14" t="n">
-        <v>281</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
@@ -1100,7 +1100,7 @@
         <v>0.4495</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2241</v>
+        <v>0.1926</v>
       </c>
       <c r="E15" t="n">
         <v>1.5977</v>
@@ -1146,7 +1146,7 @@
         <v>0.4215</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1839</v>
+        <v>0.153</v>
       </c>
       <c r="E16" t="n">
         <v>1.4982</v>
@@ -1192,7 +1192,7 @@
         <v>0.4036</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1582</v>
+        <v>0.1276</v>
       </c>
       <c r="E17" t="n">
         <v>1.4346</v>
@@ -1238,7 +1238,7 @@
         <v>0.328</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0496</v>
+        <v>0.0205</v>
       </c>
       <c r="E18" t="n">
         <v>1.1658</v>
@@ -1284,7 +1284,7 @@
         <v>0.3046</v>
       </c>
       <c r="D19" t="n">
-        <v>0.016</v>
+        <v>-0.0126</v>
       </c>
       <c r="E19" t="n">
         <v>1.0826</v>
@@ -1330,7 +1330,7 @@
         <v>0.288</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0078</v>
+        <v>-0.0361</v>
       </c>
       <c r="E20" t="n">
         <v>1.0237</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9082</v>
+        <v>0.9094</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2555</v>
+        <v>0.2558</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0545</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9082</v>
+        <v>0.9094</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1236</v>
+        <v>1.1248</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2154</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1236</v>
+        <v>1.1248</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9107</v>
+        <v>0.9117</v>
       </c>
       <c r="J21" t="n">
         <v>-0.2154</v>
@@ -1403,7 +1403,7 @@
         <v>57</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6952999999999999</v>
+        <v>0.6962999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>138</v>
@@ -1422,7 +1422,7 @@
         <v>0.0883</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2946</v>
+        <v>-0.3189</v>
       </c>
       <c r="E22" t="n">
         <v>0.3139</v>
@@ -1468,7 +1468,7 @@
         <v>0.0163</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.398</v>
+        <v>-0.4209</v>
       </c>
       <c r="E23" t="n">
         <v>0.0578</v>
@@ -1514,7 +1514,7 @@
         <v>-0.0377</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4755</v>
+        <v>-0.4973</v>
       </c>
       <c r="E24" t="n">
         <v>-0.1339</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0404</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4794</v>
+        <v>-0.5011</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1436</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0731</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5264</v>
+        <v>-0.5475</v>
       </c>
       <c r="E26" t="n">
         <v>-0.2599</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1127</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.6035</v>
       </c>
       <c r="E27" t="n">
         <v>-0.4007</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1318</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6106</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4684</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1323</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6313</v>
       </c>
       <c r="E29" t="n">
         <v>-0.4704</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2501</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7805</v>
+        <v>-0.7981</v>
       </c>
       <c r="E30" t="n">
         <v>-0.889</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3015</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.8709</v>
       </c>
       <c r="E31" t="n">
         <v>-1.0717</v>
@@ -1882,7 +1882,7 @@
         <v>-0.305</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8593</v>
+        <v>-0.8758</v>
       </c>
       <c r="E32" t="n">
         <v>-1.0841</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3212</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8827</v>
+        <v>-0.8988</v>
       </c>
       <c r="E33" t="n">
         <v>-1.1419</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3401</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9097</v>
+        <v>-0.9255</v>
       </c>
       <c r="E34" t="n">
         <v>-1.2089</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3766</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9621</v>
+        <v>-0.9772</v>
       </c>
       <c r="E35" t="n">
         <v>-1.3386</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3892</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9802</v>
+        <v>-0.995</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3833</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4356</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0468</v>
+        <v>-1.0608</v>
       </c>
       <c r="E37" t="n">
         <v>-1.5483</v>
@@ -2158,7 +2158,7 @@
         <v>-0.6818</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.4004</v>
+        <v>-1.4094</v>
       </c>
       <c r="E38" t="n">
         <v>-2.4235</v>
@@ -2204,7 +2204,7 @@
         <v>-0.7323</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.473</v>
+        <v>-1.481</v>
       </c>
       <c r="E39" t="n">
         <v>-2.6032</v>
@@ -2250,7 +2250,7 @@
         <v>-0.9332</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7614</v>
+        <v>-1.7654</v>
       </c>
       <c r="E40" t="n">
         <v>-3.3171</v>
@@ -2296,7 +2296,7 @@
         <v>-0.9474</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7818</v>
+        <v>-1.7856</v>
       </c>
       <c r="E41" t="n">
         <v>-3.3676</v>

--- a/database/event/4411/event_4411_evp_summary.xlsx
+++ b/database/event/4411/event_4411_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.768599999999999</v>
+        <v>8.389699999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7481</v>
+        <v>2.3602</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4479</v>
+        <v>3.1495</v>
       </c>
       <c r="E2" t="n">
-        <v>9.768599999999999</v>
+        <v>8.389699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5555</v>
+        <v>3.1436</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2131</v>
+        <v>5.2461</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5555</v>
+        <v>5.5899</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8818</v>
+        <v>2.9065</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2131</v>
+        <v>5.2461</v>
       </c>
       <c r="K2" t="n">
         <v>157</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>9.094899999999999</v>
+        <v>8.1526</v>
       </c>
       <c r="N2" t="n">
         <v>259</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9416</v>
+        <v>5.8193</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6715</v>
+        <v>1.6371</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9232</v>
+        <v>1.9891</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9416</v>
+        <v>5.8193</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6725</v>
+        <v>2.8805</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2691</v>
+        <v>2.9388</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6725</v>
+        <v>4.6627</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1661</v>
+        <v>2.4244</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2691</v>
+        <v>2.9388</v>
       </c>
       <c r="K3" t="n">
         <v>157</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4352</v>
+        <v>5.3632</v>
       </c>
       <c r="N3" t="n">
         <v>259</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0939</v>
+        <v>4.9743</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1517</v>
+        <v>1.3994</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1871</v>
+        <v>1.6076</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0939</v>
+        <v>4.9743</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4243</v>
+        <v>2.5084</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6696</v>
+        <v>2.4659</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4243</v>
+        <v>3.3518</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1545</v>
+        <v>1.7428</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6696</v>
+        <v>2.4659</v>
       </c>
       <c r="K4" t="n">
         <v>157</v>
@@ -621,7 +621,7 @@
         <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8241</v>
+        <v>4.2087</v>
       </c>
       <c r="N4" t="n">
         <v>259</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7455</v>
+        <v>3.6172</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0537</v>
+        <v>1.0176</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0483</v>
+        <v>0.995</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7455</v>
+        <v>3.6172</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7455</v>
+        <v>2.9733</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7455</v>
+        <v>4.9897</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7455</v>
+        <v>2.5944</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="K5" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7455</v>
+        <v>3.2383</v>
       </c>
       <c r="N5" t="n">
-        <v>156</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7249</v>
+        <v>3.5835</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0479</v>
+        <v>1.0081</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0401</v>
+        <v>0.9798</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7249</v>
+        <v>3.5835</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9863</v>
+        <v>2.8829</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7386</v>
+        <v>0.7006</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9863</v>
+        <v>4.6712</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4204</v>
+        <v>2.4288</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7386</v>
+        <v>0.7006</v>
       </c>
       <c r="K6" t="n">
         <v>81</v>
@@ -713,7 +713,7 @@
         <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>3.159</v>
+        <v>3.1294</v>
       </c>
       <c r="N6" t="n">
         <v>138</v>
@@ -722,127 +722,127 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3329</v>
+        <v>3.4883</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9376</v>
+        <v>0.9813</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8839</v>
+        <v>0.9368</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3329</v>
+        <v>3.4883</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6962</v>
+        <v>3.4883</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6367</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6962</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1854</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6367</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="L7" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8221</v>
+        <v>4.3</v>
       </c>
       <c r="N7" t="n">
-        <v>196</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.967</v>
+        <v>3.0723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8347</v>
+        <v>0.8643</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7381</v>
+        <v>0.749</v>
       </c>
       <c r="E8" t="n">
-        <v>2.967</v>
+        <v>3.0723</v>
       </c>
       <c r="F8" t="n">
-        <v>3.014</v>
+        <v>2.1648</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.047</v>
+        <v>0.9075</v>
       </c>
       <c r="H8" t="n">
-        <v>3.014</v>
+        <v>2.1648</v>
       </c>
       <c r="I8" t="n">
-        <v>2.443</v>
+        <v>1.1256</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.047</v>
+        <v>0.9075</v>
       </c>
       <c r="K8" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="L8" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="M8" t="n">
-        <v>2.396</v>
+        <v>2.0331</v>
       </c>
       <c r="N8" t="n">
-        <v>138</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7051</v>
+        <v>2.9914</v>
       </c>
       <c r="C9" t="n">
-        <v>0.761</v>
+        <v>0.8415</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6338</v>
+        <v>0.7125</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7051</v>
+        <v>2.9914</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9372</v>
+        <v>2.8665</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2321</v>
+        <v>0.1249</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9372</v>
+        <v>4.6133</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3807</v>
+        <v>2.3987</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2321</v>
+        <v>0.1249</v>
       </c>
       <c r="K9" t="n">
         <v>81</v>
@@ -851,7 +851,7 @@
         <v>57</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1486</v>
+        <v>2.5236</v>
       </c>
       <c r="N9" t="n">
         <v>138</v>
@@ -860,231 +860,231 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1418</v>
+        <v>2.8012</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6025</v>
+        <v>0.788</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4094</v>
+        <v>0.6266</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1418</v>
+        <v>2.8012</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1418</v>
+        <v>2.8629</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.0617</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1418</v>
+        <v>4.6008</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1418</v>
+        <v>2.3922</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.0617</v>
       </c>
       <c r="K10" t="n">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1418</v>
+        <v>2.3305</v>
       </c>
       <c r="N10" t="n">
-        <v>153</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0349</v>
+        <v>2.6805</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5725</v>
+        <v>0.7541</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3668</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0349</v>
+        <v>2.6805</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0349</v>
+        <v>2.6805</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0349</v>
+        <v>2.6805</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0349</v>
+        <v>2.6805</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0349</v>
+        <v>2.6805</v>
       </c>
       <c r="N11" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0201</v>
+        <v>2.5567</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5683</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3609</v>
+        <v>0.5162</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0201</v>
+        <v>2.5567</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1189</v>
+        <v>2.5567</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9012</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1189</v>
+        <v>2.5567</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9069</v>
+        <v>2.5567</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9012</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="L12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8081</v>
+        <v>2.5567</v>
       </c>
       <c r="N12" t="n">
-        <v>196</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9823</v>
+        <v>2.4887</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5577</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3458</v>
+        <v>0.4855</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9823</v>
+        <v>2.4887</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4313</v>
+        <v>2.4887</v>
       </c>
       <c r="G13" t="n">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4313</v>
+        <v>2.4887</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1601</v>
+        <v>2.4887</v>
       </c>
       <c r="J13" t="n">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L13" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7111</v>
+        <v>2.4887</v>
       </c>
       <c r="N13" t="n">
-        <v>281</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7489</v>
+        <v>2.43</v>
       </c>
       <c r="C14" t="n">
-        <v>0.492</v>
+        <v>0.6836</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2529</v>
+        <v>0.459</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7489</v>
+        <v>2.43</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7489</v>
+        <v>2.185</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7489</v>
+        <v>2.2123</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7489</v>
+        <v>1.1503</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="K14" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7489</v>
+        <v>1.3953</v>
       </c>
       <c r="N14" t="n">
-        <v>153</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5977</v>
+        <v>2.3393</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4495</v>
+        <v>0.6581</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1926</v>
+        <v>0.4181</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5977</v>
+        <v>2.3393</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5977</v>
+        <v>2.3393</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5977</v>
+        <v>2.3393</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5977</v>
+        <v>2.3393</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5977</v>
+        <v>2.3393</v>
       </c>
       <c r="N15" t="n">
         <v>156</v>
@@ -1136,277 +1136,277 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4982</v>
+        <v>2.327</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4215</v>
+        <v>0.6546</v>
       </c>
       <c r="D16" t="n">
-        <v>0.153</v>
+        <v>0.4125</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4982</v>
+        <v>2.327</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0895</v>
+        <v>2.3168</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5913</v>
+        <v>0.0102</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0895</v>
+        <v>2.6768</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6936</v>
+        <v>1.3918</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5913</v>
+        <v>0.0102</v>
       </c>
       <c r="K16" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="L16" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1023</v>
+        <v>1.402</v>
       </c>
       <c r="N16" t="n">
-        <v>196</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4346</v>
+        <v>2.2467</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4036</v>
+        <v>0.632</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1276</v>
+        <v>0.3763</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4346</v>
+        <v>2.2467</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4346</v>
+        <v>2.2467</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4346</v>
+        <v>2.2467</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4346</v>
+        <v>2.2467</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4346</v>
+        <v>2.2467</v>
       </c>
       <c r="N17" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1658</v>
+        <v>2.2232</v>
       </c>
       <c r="C18" t="n">
-        <v>0.328</v>
+        <v>0.6254</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0205</v>
+        <v>0.3656</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1658</v>
+        <v>2.2232</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1658</v>
+        <v>2.5741</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.3509</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1658</v>
+        <v>3.5832</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1658</v>
+        <v>1.8631</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.3509</v>
       </c>
       <c r="K18" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1658</v>
+        <v>1.5122</v>
       </c>
       <c r="N18" t="n">
-        <v>156</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0826</v>
+        <v>1.8473</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3046</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0126</v>
+        <v>0.1959</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0826</v>
+        <v>1.8473</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0826</v>
+        <v>1.984</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.1367</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0826</v>
+        <v>1.984</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0826</v>
+        <v>1.0316</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.1367</v>
       </c>
       <c r="K19" t="n">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0826</v>
+        <v>0.8949</v>
       </c>
       <c r="N19" t="n">
-        <v>153</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0237</v>
+        <v>1.5898</v>
       </c>
       <c r="C20" t="n">
-        <v>0.288</v>
+        <v>0.4472</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0361</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0237</v>
+        <v>1.5898</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1553</v>
+        <v>1.5898</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1316</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1553</v>
+        <v>1.5898</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9364</v>
+        <v>1.5898</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1316</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="L20" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8048</v>
+        <v>1.5898</v>
       </c>
       <c r="N20" t="n">
-        <v>259</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9094</v>
+        <v>1.4865</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2558</v>
+        <v>0.4182</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.0331</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9094</v>
+        <v>1.4865</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1248</v>
+        <v>1.4865</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2154</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1248</v>
+        <v>1.4865</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9117</v>
+        <v>1.4865</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2154</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="L21" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6962999999999999</v>
+        <v>1.4865</v>
       </c>
       <c r="N21" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3139</v>
+        <v>0.9791</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0883</v>
+        <v>0.2754</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3189</v>
+        <v>-0.196</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3139</v>
+        <v>0.9791</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3265</v>
+        <v>0.848</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0126</v>
+        <v>0.1311</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3265</v>
+        <v>0.848</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2646</v>
+        <v>0.4409</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0126</v>
+        <v>0.1311</v>
       </c>
       <c r="K22" t="n">
         <v>127</v>
@@ -1449,7 +1449,7 @@
         <v>69</v>
       </c>
       <c r="M22" t="n">
-        <v>0.252</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>196</v>
@@ -1458,277 +1458,277 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0578</v>
+        <v>0.3173</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0163</v>
+        <v>0.0893</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4209</v>
+        <v>-0.4948</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0578</v>
+        <v>0.3173</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0578</v>
+        <v>-0.0371</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.3544</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0578</v>
+        <v>-0.0371</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0578</v>
+        <v>-0.0193</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.3544</v>
       </c>
       <c r="K23" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0578</v>
+        <v>0.3351</v>
       </c>
       <c r="N23" t="n">
-        <v>123</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1339</v>
+        <v>0.2474</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0377</v>
+        <v>0.0696</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4973</v>
+        <v>-0.5263</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1339</v>
+        <v>0.2474</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1339</v>
+        <v>0.2474</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1339</v>
+        <v>0.2474</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1339</v>
+        <v>0.2474</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1339</v>
+        <v>0.2474</v>
       </c>
       <c r="N24" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1436</v>
+        <v>0.2402</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0404</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5011</v>
+        <v>-0.5296</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1436</v>
+        <v>0.2402</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4218</v>
+        <v>0.2402</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2782</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4218</v>
+        <v>0.2402</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3419</v>
+        <v>0.2402</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2782</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="L25" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.06369999999999998</v>
+        <v>0.2402</v>
       </c>
       <c r="N25" t="n">
-        <v>196</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2599</v>
+        <v>0.0523</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0731</v>
+        <v>0.0147</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5475</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2599</v>
+        <v>0.0523</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.125</v>
+        <v>0.0523</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1349</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.125</v>
+        <v>0.0523</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1013</v>
+        <v>0.0523</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1349</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="L26" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2362</v>
+        <v>0.0523</v>
       </c>
       <c r="N26" t="n">
-        <v>281</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4007</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1127</v>
+        <v>0.0023</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6035</v>
+        <v>-0.6343</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4007</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4007</v>
+        <v>0.1198</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.1116</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4007</v>
+        <v>0.1198</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4007</v>
+        <v>0.0623</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.1116</v>
       </c>
       <c r="K27" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4007</v>
+        <v>-0.0493</v>
       </c>
       <c r="N27" t="n">
-        <v>156</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4684</v>
+        <v>-0.0582</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1318</v>
+        <v>-0.0164</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6643</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4684</v>
+        <v>-0.0582</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4684</v>
+        <v>1.4651</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-1.5233</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4684</v>
+        <v>1.4651</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4684</v>
+        <v>0.7618</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-1.5233</v>
       </c>
       <c r="K28" t="n">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4684</v>
+        <v>-0.7615000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>70</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4704</v>
+        <v>-0.1049</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1323</v>
+        <v>-0.0295</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6313</v>
+        <v>-0.6854</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4704</v>
+        <v>-0.1049</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4704</v>
+        <v>-0.1049</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4704</v>
+        <v>-0.1049</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4704</v>
+        <v>-0.1049</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4704</v>
+        <v>-0.1049</v>
       </c>
       <c r="N29" t="n">
         <v>123</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.889</v>
+        <v>-0.2663</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2501</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7981</v>
+        <v>-0.7582</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.889</v>
+        <v>-0.2663</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.889</v>
+        <v>-0.2663</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.889</v>
+        <v>-0.2663</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.889</v>
+        <v>-0.2663</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.889</v>
+        <v>-0.2663</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
@@ -1826,277 +1826,277 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0717</v>
+        <v>-0.4824</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3015</v>
+        <v>-0.1357</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8709</v>
+        <v>-0.8558</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0717</v>
+        <v>-0.4824</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0717</v>
+        <v>-0.4824</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0717</v>
+        <v>-0.4824</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0717</v>
+        <v>-0.4824</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.0717</v>
+        <v>-0.4824</v>
       </c>
       <c r="N31" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0841</v>
+        <v>-0.6353</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.305</v>
+        <v>-0.1787</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8758</v>
+        <v>-0.9248</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0841</v>
+        <v>-0.6353</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.0841</v>
+        <v>-0.6353</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.0841</v>
+        <v>-0.6353</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.0841</v>
+        <v>-0.6353</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.0841</v>
+        <v>-0.6353</v>
       </c>
       <c r="N32" t="n">
-        <v>123</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.1419</v>
+        <v>-0.6368</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3212</v>
+        <v>-0.1791</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8988</v>
+        <v>-0.9255</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.1419</v>
+        <v>-0.6368</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.1419</v>
+        <v>-0.6368</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.1419</v>
+        <v>-0.6368</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.1419</v>
+        <v>-0.6368</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.1419</v>
+        <v>-0.6368</v>
       </c>
       <c r="N33" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.2089</v>
+        <v>-0.6746</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3401</v>
+        <v>-0.1898</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9255</v>
+        <v>-0.9426</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.2089</v>
+        <v>-0.6746</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.2089</v>
+        <v>-0.6746</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.2089</v>
+        <v>-0.6746</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.2089</v>
+        <v>-0.6746</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.2089</v>
+        <v>-0.6746</v>
       </c>
       <c r="N34" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3386</v>
+        <v>-0.7721</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3766</v>
+        <v>-0.2172</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9772</v>
+        <v>-0.9866</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3386</v>
+        <v>-0.7721</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3386</v>
+        <v>-0.7721</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3386</v>
+        <v>-0.7721</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3386</v>
+        <v>-0.7721</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.3386</v>
+        <v>-0.7721</v>
       </c>
       <c r="N35" t="n">
-        <v>70</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3833</v>
+        <v>-1.1006</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3892</v>
+        <v>-0.3096</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.995</v>
+        <v>-1.1349</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3833</v>
+        <v>-1.1006</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3385</v>
+        <v>-1.1006</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.7218</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3385</v>
+        <v>-1.1006</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2744</v>
+        <v>-1.1006</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.7218</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>167</v>
+        <v>70</v>
       </c>
       <c r="L36" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.4474</v>
+        <v>-1.1006</v>
       </c>
       <c r="N36" t="n">
-        <v>281</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5483</v>
+        <v>-1.2895</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4356</v>
+        <v>-0.3628</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0608</v>
+        <v>-1.2202</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5483</v>
+        <v>-1.2895</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.5483</v>
+        <v>-1.2895</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.5483</v>
+        <v>-1.2895</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.5483</v>
+        <v>-1.2895</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.5483</v>
+        <v>-1.2895</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.4235</v>
+        <v>-2.6024</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6818</v>
+        <v>-0.7321</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.4094</v>
+        <v>-1.8129</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.4235</v>
+        <v>-2.6024</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.2557</v>
+        <v>-2.3258</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1678</v>
+        <v>-0.2766</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.2557</v>
+        <v>-2.3258</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.8283</v>
+        <v>-1.2093</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1678</v>
+        <v>-0.2766</v>
       </c>
       <c r="K38" t="n">
         <v>167</v>
@@ -2185,7 +2185,7 @@
         <v>114</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.9961</v>
+        <v>-1.4859</v>
       </c>
       <c r="N38" t="n">
         <v>281</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>ableJ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.6032</v>
+        <v>-2.9339</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7323</v>
+        <v>-0.8254</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.481</v>
+        <v>-1.9625</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.6032</v>
+        <v>-2.9339</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.0358</v>
+        <v>-1.3128</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5674</v>
+        <v>-1.6211</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.0358</v>
+        <v>-1.3128</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6501</v>
+        <v>-0.6826</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5674</v>
+        <v>-1.6211</v>
       </c>
       <c r="K39" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="L39" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.2175</v>
+        <v>-2.3037</v>
       </c>
       <c r="N39" t="n">
-        <v>259</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ableJ</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.3171</v>
+        <v>-3.007</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9332</v>
+        <v>-0.8459</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7654</v>
+        <v>-1.9955</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.3171</v>
+        <v>-3.007</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4081</v>
+        <v>-2.4618</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.909</v>
+        <v>-0.5452</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4081</v>
+        <v>-2.4618</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1413</v>
+        <v>-1.28</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.909</v>
+        <v>-0.5452</v>
       </c>
       <c r="K40" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L40" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.0503</v>
+        <v>-1.8252</v>
       </c>
       <c r="N40" t="n">
-        <v>281</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.3676</v>
+        <v>-4.4275</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9474</v>
+        <v>-1.2456</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7856</v>
+        <v>-2.6368</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.3676</v>
+        <v>-4.4275</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.7556</v>
+        <v>-4.0448</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.612</v>
+        <v>-0.3827</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.7556</v>
+        <v>-4.0448</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2335</v>
+        <v>-2.1031</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.612</v>
+        <v>-0.3827</v>
       </c>
       <c r="K41" t="n">
         <v>81</v>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8455</v>
+        <v>-2.4858</v>
       </c>
       <c r="N41" t="n">
         <v>138</v>
@@ -2429,10 +2429,10 @@
         <v>1.03</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1583</v>
+        <v>0.1363</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9575</v>
+        <v>3.4075</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.99</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0417</v>
+        <v>-0.0004</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0425</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3335</v>
+        <v>-0.22</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.3375</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.75</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4118</v>
+        <v>-0.2687</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.295</v>
+        <v>-6.7175</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.65</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5526</v>
+        <v>-0.364</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.815</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.56</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3088</v>
+        <v>1.2015</v>
       </c>
       <c r="J7" t="n">
-        <v>32.72</v>
+        <v>30.0375</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.45</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0875</v>
+        <v>1.0632</v>
       </c>
       <c r="J8" t="n">
-        <v>27.1875</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7502</v>
+        <v>0.778</v>
       </c>
       <c r="J9" t="n">
-        <v>18.755</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.27</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.7113</v>
       </c>
       <c r="J10" t="n">
-        <v>16.7225</v>
+        <v>17.7825</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.75</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8589</v>
+        <v>-0.8163</v>
       </c>
       <c r="J11" t="n">
-        <v>-21.4725</v>
+        <v>-20.4075</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.8</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1895</v>
+        <v>-0.1735</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.79</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2673</v>
+        <v>-0.2283</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.346</v>
+        <v>-4.566</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.57</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5755</v>
+        <v>-0.4011</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.51</v>
+        <v>-8.022</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.47</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7229</v>
+        <v>-0.4944</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.458</v>
+        <v>-9.888</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.44</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7635</v>
+        <v>-0.5229</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.27</v>
+        <v>-10.458</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>2.14</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1028</v>
+        <v>1.8266</v>
       </c>
       <c r="J17" t="n">
-        <v>42.056</v>
+        <v>36.532</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.56</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2152</v>
+        <v>1.1673</v>
       </c>
       <c r="J18" t="n">
-        <v>24.304</v>
+        <v>23.346</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6687</v>
+        <v>0.7883</v>
       </c>
       <c r="J19" t="n">
-        <v>13.374</v>
+        <v>15.766</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.18</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3488</v>
+        <v>0.4565</v>
       </c>
       <c r="J20" t="n">
-        <v>6.976</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.12</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1995</v>
+        <v>0.2989</v>
       </c>
       <c r="J21" t="n">
-        <v>3.99</v>
+        <v>5.978</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>0.878</v>
+        <v>0.7943</v>
       </c>
       <c r="J22" t="n">
-        <v>29.852</v>
+        <v>27.0062</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3628</v>
+        <v>0.3855</v>
       </c>
       <c r="J23" t="n">
-        <v>12.3352</v>
+        <v>13.107</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1932</v>
+        <v>-0.1064</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.5688</v>
+        <v>-3.6176</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.79</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4104</v>
+        <v>-0.2557</v>
       </c>
       <c r="J25" t="n">
-        <v>-13.9536</v>
+        <v>-8.6938</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4515</v>
+        <v>-0.2852</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.351</v>
+        <v>-9.6968</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6524</v>
+        <v>1.1527</v>
       </c>
       <c r="J27" t="n">
-        <v>56.1816</v>
+        <v>39.1918</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.6232</v>
       </c>
       <c r="J28" t="n">
-        <v>28.2574</v>
+        <v>21.1888</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.27</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7369</v>
+        <v>0.5682</v>
       </c>
       <c r="J29" t="n">
-        <v>25.0546</v>
+        <v>19.3188</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6989</v>
+        <v>-0.6424</v>
       </c>
       <c r="J30" t="n">
-        <v>-23.7626</v>
+        <v>-21.8416</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8389</v>
+        <v>-0.7953</v>
       </c>
       <c r="J31" t="n">
-        <v>-28.5226</v>
+        <v>-27.0402</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.08</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2194</v>
+        <v>0.2235</v>
       </c>
       <c r="J32" t="n">
-        <v>5.0462</v>
+        <v>5.1405</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.98</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0222</v>
+        <v>-0.0303</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.6969</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.93</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1394</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.2062</v>
+        <v>-2.1551</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2016</v>
+        <v>-0.127</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.6368</v>
+        <v>-2.921</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4098</v>
+        <v>-0.2606</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.4254</v>
+        <v>-5.9938</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.74</v>
       </c>
       <c r="I37" t="n">
-        <v>1.6484</v>
+        <v>1.1508</v>
       </c>
       <c r="J37" t="n">
-        <v>37.9132</v>
+        <v>26.4684</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.46</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1133</v>
+        <v>0.8043</v>
       </c>
       <c r="J38" t="n">
-        <v>25.6059</v>
+        <v>18.4989</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.31</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7816</v>
+        <v>0.6099</v>
       </c>
       <c r="J39" t="n">
-        <v>17.9768</v>
+        <v>14.0277</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.91</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4642</v>
+        <v>-0.3878</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.6766</v>
+        <v>-8.9194</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5968</v>
+        <v>-0.5293</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.7264</v>
+        <v>-12.1739</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4786</v>
+        <v>0.4709</v>
       </c>
       <c r="J42" t="n">
-        <v>12.9222</v>
+        <v>12.7143</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3676</v>
+        <v>0.3877</v>
       </c>
       <c r="J43" t="n">
-        <v>9.9252</v>
+        <v>10.4679</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0828</v>
+        <v>0.1097</v>
       </c>
       <c r="J44" t="n">
-        <v>2.2356</v>
+        <v>2.9619</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1708</v>
+        <v>-0.093</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.6116</v>
+        <v>-2.511</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.77</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4354</v>
+        <v>-0.274</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.7558</v>
+        <v>-7.398</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2378</v>
+        <v>0.8706</v>
       </c>
       <c r="J47" t="n">
-        <v>33.4206</v>
+        <v>23.5062</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.21</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6816</v>
+        <v>0.5137</v>
       </c>
       <c r="J48" t="n">
-        <v>18.4032</v>
+        <v>13.8699</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.82</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6241</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>-16.8507</v>
+        <v>-15.5007</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6495</v>
+        <v>-0.6004</v>
       </c>
       <c r="J50" t="n">
-        <v>-17.5365</v>
+        <v>-16.2108</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.79</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6993</v>
+        <v>-0.6525</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.8811</v>
+        <v>-17.6175</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5342</v>
       </c>
       <c r="J52" t="n">
-        <v>23.2638</v>
+        <v>22.4364</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.26</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4226</v>
+        <v>0.4366</v>
       </c>
       <c r="J53" t="n">
-        <v>17.7492</v>
+        <v>18.3372</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1582</v>
+        <v>0.2241</v>
       </c>
       <c r="J54" t="n">
-        <v>6.6444</v>
+        <v>9.4122</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.0333</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.7548</v>
+        <v>-1.3986</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1559</v>
+        <v>-0.0769</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.5478</v>
+        <v>-3.2298</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.44</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2238</v>
+        <v>0.8613</v>
       </c>
       <c r="J57" t="n">
-        <v>51.3996</v>
+        <v>36.1746</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.03</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1835</v>
+        <v>0.1378</v>
       </c>
       <c r="J58" t="n">
-        <v>7.707</v>
+        <v>5.7876</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.83</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5778</v>
+        <v>-0.5336</v>
       </c>
       <c r="J59" t="n">
-        <v>-24.2676</v>
+        <v>-22.4112</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.82</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6041</v>
+        <v>-0.5601</v>
       </c>
       <c r="J60" t="n">
-        <v>-25.3722</v>
+        <v>-23.5242</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8028</v>
+        <v>-0.7659</v>
       </c>
       <c r="J61" t="n">
-        <v>-33.7176</v>
+        <v>-32.1678</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.42</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0611</v>
+        <v>1.0379</v>
       </c>
       <c r="J62" t="n">
-        <v>30.7719</v>
+        <v>30.0991</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9756</v>
+        <v>0.9712</v>
       </c>
       <c r="J63" t="n">
-        <v>28.2924</v>
+        <v>28.1648</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.31</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8187</v>
+        <v>0.8182</v>
       </c>
       <c r="J64" t="n">
-        <v>23.7423</v>
+        <v>23.7278</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.13</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3252</v>
+        <v>0.386</v>
       </c>
       <c r="J65" t="n">
-        <v>9.4308</v>
+        <v>11.194</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.85</v>
       </c>
       <c r="J66" t="n">
-        <v>-25.7694</v>
+        <v>-24.65</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.19</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3804</v>
+        <v>0.4309</v>
       </c>
       <c r="J67" t="n">
-        <v>11.0316</v>
+        <v>12.4961</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.96</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0973</v>
+        <v>-0.0605</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.8217</v>
+        <v>-1.7545</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1614</v>
+        <v>-0.0968</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.6806</v>
+        <v>-2.8072</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.2901</v>
+        <v>-3.7903</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.284</v>
+        <v>-0.1738</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.236000000000001</v>
+        <v>-5.0402</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2366</v>
+        <v>1.1585</v>
       </c>
       <c r="J72" t="n">
-        <v>29.6784</v>
+        <v>27.804</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9881</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>23.7144</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.32</v>
       </c>
       <c r="I74" t="n">
-        <v>0.78</v>
+        <v>0.8171</v>
       </c>
       <c r="J74" t="n">
-        <v>18.72</v>
+        <v>19.6104</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.26</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6105</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>14.652</v>
+        <v>16.44</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.95</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3563</v>
+        <v>-0.2731</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.5512</v>
+        <v>-6.5544</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.11</v>
       </c>
       <c r="I77" t="n">
-        <v>0.281</v>
+        <v>0.2967</v>
       </c>
       <c r="J77" t="n">
-        <v>6.744</v>
+        <v>7.1208</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1113</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>2.6712</v>
+        <v>2.1216</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0861</v>
+        <v>0.0589</v>
       </c>
       <c r="J79" t="n">
-        <v>2.0664</v>
+        <v>1.4136</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.096</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.304</v>
+        <v>-1.9128</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.44</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8214</v>
+        <v>-0.5638</v>
       </c>
       <c r="J81" t="n">
-        <v>-19.7136</v>
+        <v>-13.5312</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.16</v>
       </c>
       <c r="I82" t="n">
-        <v>0.384</v>
+        <v>0.3269</v>
       </c>
       <c r="J82" t="n">
-        <v>10.752</v>
+        <v>9.1532</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2005</v>
+        <v>0.1442</v>
       </c>
       <c r="J83" t="n">
-        <v>5.614</v>
+        <v>4.0376</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.86</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2134</v>
+        <v>-0.1607</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.9752</v>
+        <v>-4.4996</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.71</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4688</v>
+        <v>-0.3066</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.1264</v>
+        <v>-8.5848</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.42</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.8363</v>
+        <v>-0.5752</v>
       </c>
       <c r="J86" t="n">
-        <v>-23.4164</v>
+        <v>-16.1056</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6692</v>
+        <v>0.5893</v>
       </c>
       <c r="J87" t="n">
-        <v>18.7376</v>
+        <v>16.5004</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.24</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3875</v>
+        <v>0.3346</v>
       </c>
       <c r="J88" t="n">
-        <v>10.85</v>
+        <v>9.3688</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3125</v>
+        <v>0.2735</v>
       </c>
       <c r="J89" t="n">
-        <v>8.75</v>
+        <v>7.658</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0604</v>
+        <v>-0.0142</v>
       </c>
       <c r="J90" t="n">
-        <v>-1.6912</v>
+        <v>-0.3976</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2968</v>
+        <v>-0.1727</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.3104</v>
+        <v>-4.8356</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6452</v>
       </c>
       <c r="J92" t="n">
-        <v>17.94</v>
+        <v>16.7752</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0005</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.2184</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1221</v>
+        <v>-0.0944</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.1746</v>
+        <v>-2.4544</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2728</v>
+        <v>-0.2301</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.0928</v>
+        <v>-5.9826</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.89</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4281</v>
+        <v>-0.3787</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.1306</v>
+        <v>-9.8462</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.49</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7536</v>
+        <v>0.9371</v>
       </c>
       <c r="J97" t="n">
-        <v>19.5936</v>
+        <v>24.3646</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2463</v>
+        <v>0.2677</v>
       </c>
       <c r="J98" t="n">
-        <v>6.4038</v>
+        <v>6.9602</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0703</v>
+        <v>0.0667</v>
       </c>
       <c r="J99" t="n">
-        <v>1.8278</v>
+        <v>1.7342</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2601</v>
+        <v>-0.1557</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.7626</v>
+        <v>-4.0482</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.48</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7862</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="J101" t="n">
-        <v>-20.4412</v>
+        <v>-13.9568</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6732</v>
+        <v>0.633</v>
       </c>
       <c r="J102" t="n">
-        <v>19.5228</v>
+        <v>18.357</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.09</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3436</v>
+        <v>0.3098</v>
       </c>
       <c r="J103" t="n">
-        <v>9.964399999999999</v>
+        <v>8.9842</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1196</v>
+        <v>0.124</v>
       </c>
       <c r="J104" t="n">
-        <v>3.4684</v>
+        <v>3.596</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2896</v>
+        <v>-0.2377</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.398400000000001</v>
+        <v>-6.8933</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.89</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4419</v>
+        <v>-0.3868</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.8151</v>
+        <v>-11.2172</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.4</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6269</v>
+        <v>0.7642</v>
       </c>
       <c r="J107" t="n">
-        <v>18.1801</v>
+        <v>22.1618</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.6476</v>
       </c>
       <c r="J108" t="n">
-        <v>15.6542</v>
+        <v>18.7804</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.92</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2103</v>
+        <v>-0.1179</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.0987</v>
+        <v>-3.4191</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3381</v>
+        <v>-0.2049</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.8049</v>
+        <v>-5.9421</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.396</v>
+        <v>-0.2456</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.484</v>
+        <v>-7.1224</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.82</v>
       </c>
       <c r="I112" t="n">
-        <v>1.7104</v>
+        <v>1.473</v>
       </c>
       <c r="J112" t="n">
-        <v>34.208</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.6</v>
       </c>
       <c r="I113" t="n">
-        <v>1.3054</v>
+        <v>1.2175</v>
       </c>
       <c r="J113" t="n">
-        <v>26.108</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.33</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6997</v>
+        <v>0.8149</v>
       </c>
       <c r="J114" t="n">
-        <v>13.994</v>
+        <v>16.298</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.3</v>
       </c>
       <c r="I115" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.7477</v>
       </c>
       <c r="J115" t="n">
-        <v>12.652</v>
+        <v>14.954</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.16</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3063</v>
+        <v>0.4099</v>
       </c>
       <c r="J116" t="n">
-        <v>6.126</v>
+        <v>8.198</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.89</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0604</v>
+        <v>-0.0795</v>
       </c>
       <c r="J117" t="n">
-        <v>-1.208</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.63</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.4943</v>
+        <v>-0.3521</v>
       </c>
       <c r="J118" t="n">
-        <v>-9.885999999999999</v>
+        <v>-7.042</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.63</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4943</v>
+        <v>-0.3521</v>
       </c>
       <c r="J119" t="n">
-        <v>-9.885999999999999</v>
+        <v>-7.042</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.54</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6371</v>
+        <v>-0.4345</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.742</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.5</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.4721</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.86</v>
+        <v>-9.442</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.34</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5777</v>
+        <v>0.5308</v>
       </c>
       <c r="J122" t="n">
-        <v>14.4425</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0774</v>
+        <v>0.0529</v>
       </c>
       <c r="J123" t="n">
-        <v>1.935</v>
+        <v>1.3225</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0824</v>
+        <v>-0.0485</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.06</v>
+        <v>-1.2125</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2391</v>
+        <v>-0.1432</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.9775</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.53</v>
+        <v>-0.3437</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.25</v>
+        <v>-8.592499999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.27</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4343</v>
+        <v>0.3728</v>
       </c>
       <c r="J127" t="n">
-        <v>10.8575</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3781</v>
+        <v>0.3245</v>
       </c>
       <c r="J128" t="n">
-        <v>9.452500000000001</v>
+        <v>8.112500000000001</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2696</v>
+        <v>0.2375</v>
       </c>
       <c r="J129" t="n">
-        <v>6.74</v>
+        <v>5.9375</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0238</v>
+        <v>0.0501</v>
       </c>
       <c r="J130" t="n">
-        <v>0.595</v>
+        <v>1.2525</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.01</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0229</v>
+        <v>0.0108</v>
       </c>
       <c r="J131" t="n">
-        <v>-0.5725</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.4</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0853</v>
+        <v>1.0444</v>
       </c>
       <c r="J132" t="n">
-        <v>32.559</v>
+        <v>31.332</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8433</v>
+        <v>0.8164</v>
       </c>
       <c r="J133" t="n">
-        <v>25.299</v>
+        <v>24.492</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.03</v>
       </c>
       <c r="I134" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="J134" t="n">
-        <v>2.52</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0435</v>
+        <v>0.0805</v>
       </c>
       <c r="J135" t="n">
-        <v>1.305</v>
+        <v>2.415</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.1394</v>
+        <v>-1.1327</v>
       </c>
       <c r="J136" t="n">
-        <v>-34.182</v>
+        <v>-33.981</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.43</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6714</v>
+        <v>0.8238</v>
       </c>
       <c r="J137" t="n">
-        <v>20.142</v>
+        <v>24.714</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.14</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2816</v>
+        <v>0.3173</v>
       </c>
       <c r="J138" t="n">
-        <v>8.448</v>
+        <v>9.519</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.203</v>
+        <v>-0.1151</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.09</v>
+        <v>-3.453</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2861</v>
+        <v>-0.1705</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.583</v>
+        <v>-5.115</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.8</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3907</v>
+        <v>-0.2427</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.721</v>
+        <v>-7.281</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.9</v>
       </c>
       <c r="I142" t="n">
-        <v>1.8158</v>
+        <v>1.5469</v>
       </c>
       <c r="J142" t="n">
-        <v>38.1318</v>
+        <v>32.4849</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.87</v>
       </c>
       <c r="I143" t="n">
-        <v>1.7644</v>
+        <v>1.5134</v>
       </c>
       <c r="J143" t="n">
-        <v>37.0524</v>
+        <v>31.7814</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.57</v>
       </c>
       <c r="I144" t="n">
-        <v>1.2039</v>
+        <v>1.1724</v>
       </c>
       <c r="J144" t="n">
-        <v>25.2819</v>
+        <v>24.6204</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.29</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5825</v>
+        <v>0.7085</v>
       </c>
       <c r="J145" t="n">
-        <v>12.2325</v>
+        <v>14.8785</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.99</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2645</v>
+        <v>-0.1742</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.5545</v>
+        <v>-3.6582</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.82</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.1409</v>
+        <v>-0.1387</v>
       </c>
       <c r="J147" t="n">
-        <v>-2.9589</v>
+        <v>-2.9127</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.64</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.4204</v>
+        <v>-0.3325</v>
       </c>
       <c r="J148" t="n">
-        <v>-8.8284</v>
+        <v>-6.9825</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.6</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4866</v>
+        <v>-0.3704</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.2186</v>
+        <v>-7.7784</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.49</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6823</v>
+        <v>-0.4696</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.3283</v>
+        <v>-9.861599999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.33</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8984</v>
+        <v>-0.6231</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.8664</v>
+        <v>-13.0851</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.66</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4714</v>
+        <v>1.3104</v>
       </c>
       <c r="J152" t="n">
-        <v>32.3708</v>
+        <v>28.8288</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.39</v>
       </c>
       <c r="I153" t="n">
-        <v>0.9258</v>
+        <v>0.9584</v>
       </c>
       <c r="J153" t="n">
-        <v>20.3676</v>
+        <v>21.0848</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.36</v>
       </c>
       <c r="I154" t="n">
-        <v>0.8556</v>
+        <v>0.898</v>
       </c>
       <c r="J154" t="n">
-        <v>18.8232</v>
+        <v>19.756</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2928</v>
+        <v>0.3828</v>
       </c>
       <c r="J155" t="n">
-        <v>6.4416</v>
+        <v>8.4216</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.08</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1294</v>
+        <v>0.2151</v>
       </c>
       <c r="J156" t="n">
-        <v>2.8468</v>
+        <v>4.7322</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3894</v>
+        <v>0.4419</v>
       </c>
       <c r="J157" t="n">
-        <v>8.566800000000001</v>
+        <v>9.7218</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.72</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.3627</v>
+        <v>-0.2777</v>
       </c>
       <c r="J158" t="n">
-        <v>-7.9794</v>
+        <v>-6.1094</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.62</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.3686</v>
       </c>
       <c r="J159" t="n">
-        <v>-11.9196</v>
+        <v>-8.1092</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.52</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6823</v>
+        <v>-0.4621</v>
       </c>
       <c r="J160" t="n">
-        <v>-15.0106</v>
+        <v>-10.1662</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.46</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7604</v>
+        <v>-0.5183</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.7288</v>
+        <v>-11.4026</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4875</v>
+        <v>0.416</v>
       </c>
       <c r="J162" t="n">
-        <v>14.1375</v>
+        <v>12.064</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.29</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4743</v>
+        <v>0.404</v>
       </c>
       <c r="J163" t="n">
-        <v>13.7547</v>
+        <v>11.716</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.08</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1365</v>
+        <v>0.1345</v>
       </c>
       <c r="J164" t="n">
-        <v>3.9585</v>
+        <v>3.9005</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1855</v>
+        <v>-0.0987</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.3795</v>
+        <v>-2.8623</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2704</v>
+        <v>-0.1562</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.8416</v>
+        <v>-4.5298</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.29</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5181</v>
+        <v>0.4686</v>
       </c>
       <c r="J167" t="n">
-        <v>15.0249</v>
+        <v>13.5894</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I168" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0551</v>
       </c>
       <c r="J168" t="n">
-        <v>2.436</v>
+        <v>1.5979</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2678</v>
+        <v>-0.1632</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.7662</v>
+        <v>-4.7328</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.86</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.284</v>
+        <v>-0.1738</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.236000000000001</v>
+        <v>-5.0402</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3758</v>
+        <v>-0.2352</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.8982</v>
+        <v>-6.8208</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5598</v>
+        <v>0.6686</v>
       </c>
       <c r="J172" t="n">
-        <v>15.1146</v>
+        <v>18.0522</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1718</v>
+        <v>0.1713</v>
       </c>
       <c r="J173" t="n">
-        <v>4.6386</v>
+        <v>4.6251</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0261</v>
+        <v>0.0061</v>
       </c>
       <c r="J174" t="n">
-        <v>0.7047</v>
+        <v>0.1647</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.74</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4587</v>
+        <v>-0.2933</v>
       </c>
       <c r="J175" t="n">
-        <v>-12.3849</v>
+        <v>-7.9191</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.3505</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.5476</v>
+        <v>-9.4635</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.55</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3288</v>
+        <v>1.2094</v>
       </c>
       <c r="J177" t="n">
-        <v>35.8776</v>
+        <v>32.6538</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8474</v>
+        <v>0.8442</v>
       </c>
       <c r="J178" t="n">
-        <v>22.8798</v>
+        <v>22.7934</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1541</v>
+        <v>0.2188</v>
       </c>
       <c r="J179" t="n">
-        <v>4.1607</v>
+        <v>5.9076</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0164</v>
+        <v>0.0514</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.4428</v>
+        <v>1.3878</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2901</v>
+        <v>-0.213</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.8327</v>
+        <v>-5.751</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.85</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1434</v>
+        <v>-0.1377</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.2982</v>
+        <v>-3.1671</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.82</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1919</v>
+        <v>-0.1713</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.4137</v>
+        <v>-3.9399</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.71</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3677</v>
+        <v>-0.2843</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.457100000000001</v>
+        <v>-6.5389</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.51</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.6901</v>
+        <v>-0.4684</v>
       </c>
       <c r="J185" t="n">
-        <v>-15.8723</v>
+        <v>-10.7732</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.46</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7558</v>
+        <v>-0.5153</v>
       </c>
       <c r="J186" t="n">
-        <v>-17.3834</v>
+        <v>-11.8519</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.66</v>
       </c>
       <c r="I187" t="n">
-        <v>1.4777</v>
+        <v>1.3135</v>
       </c>
       <c r="J187" t="n">
-        <v>33.9871</v>
+        <v>30.2105</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.37</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8884</v>
+        <v>0.9215</v>
       </c>
       <c r="J188" t="n">
-        <v>20.4332</v>
+        <v>21.1945</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.2</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4507</v>
+        <v>0.539</v>
       </c>
       <c r="J189" t="n">
-        <v>10.3661</v>
+        <v>12.397</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4507</v>
+        <v>0.539</v>
       </c>
       <c r="J190" t="n">
-        <v>10.3661</v>
+        <v>12.397</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.13</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2717</v>
+        <v>0.3592</v>
       </c>
       <c r="J191" t="n">
-        <v>6.2491</v>
+        <v>8.2616</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5619</v>
+        <v>0.6713</v>
       </c>
       <c r="J192" t="n">
-        <v>16.2951</v>
+        <v>19.4677</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.97</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.058</v>
+        <v>-0.0467</v>
       </c>
       <c r="J193" t="n">
-        <v>-1.682</v>
+        <v>-1.3543</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.058</v>
+        <v>-0.0467</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.682</v>
+        <v>-1.3543</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.82</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3422</v>
+        <v>-0.2134</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.9238</v>
+        <v>-6.1886</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5246</v>
+        <v>-0.3404</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.2134</v>
+        <v>-9.871600000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8589</v>
+        <v>0.8423</v>
       </c>
       <c r="J197" t="n">
-        <v>24.9081</v>
+        <v>24.4267</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5663</v>
+        <v>0.5517</v>
       </c>
       <c r="J198" t="n">
-        <v>16.4227</v>
+        <v>15.9993</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.15</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4549</v>
+        <v>0.4504</v>
       </c>
       <c r="J199" t="n">
-        <v>13.1921</v>
+        <v>13.0616</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.02</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0118</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="J200" t="n">
-        <v>0.3422</v>
+        <v>1.9459</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.332</v>
+        <v>-0.2624</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.628</v>
+        <v>-7.6096</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5441</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="J202" t="n">
-        <v>13.6025</v>
+        <v>16.1925</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2943</v>
+        <v>0.3079</v>
       </c>
       <c r="J203" t="n">
-        <v>7.3575</v>
+        <v>7.6975</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4058</v>
+        <v>-0.2666</v>
       </c>
       <c r="J204" t="n">
-        <v>-10.145</v>
+        <v>-6.665</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.57</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6529</v>
+        <v>-0.4365</v>
       </c>
       <c r="J205" t="n">
-        <v>-16.3225</v>
+        <v>-10.9125</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.45</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7995</v>
+        <v>-0.5467</v>
       </c>
       <c r="J206" t="n">
-        <v>-19.9875</v>
+        <v>-13.6675</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.62</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4369</v>
+        <v>1.2828</v>
       </c>
       <c r="J207" t="n">
-        <v>35.9225</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1015</v>
+        <v>1.0689</v>
       </c>
       <c r="J208" t="n">
-        <v>27.5375</v>
+        <v>26.7225</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.24</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6096</v>
+        <v>0.6476</v>
       </c>
       <c r="J209" t="n">
-        <v>15.24</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.11</v>
       </c>
       <c r="I210" t="n">
-        <v>0.247</v>
+        <v>0.3216</v>
       </c>
       <c r="J210" t="n">
-        <v>6.175</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.77</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8082</v>
+        <v>-0.7603</v>
       </c>
       <c r="J211" t="n">
-        <v>-20.205</v>
+        <v>-19.0075</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4455</v>
+        <v>0.521</v>
       </c>
       <c r="J212" t="n">
-        <v>21.384</v>
+        <v>25.008</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.18</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3459</v>
+        <v>0.3946</v>
       </c>
       <c r="J213" t="n">
-        <v>16.6032</v>
+        <v>18.9408</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1638</v>
+        <v>-0.0906</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.8624</v>
+        <v>-4.3488</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1638</v>
+        <v>-0.0906</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.8624</v>
+        <v>-4.3488</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3746</v>
+        <v>-0.2317</v>
       </c>
       <c r="J216" t="n">
-        <v>-17.9808</v>
+        <v>-11.1216</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.24</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7489</v>
+        <v>0.7108</v>
       </c>
       <c r="J217" t="n">
-        <v>35.9472</v>
+        <v>34.1184</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0335</v>
+        <v>-0.0051</v>
       </c>
       <c r="J218" t="n">
-        <v>-1.608</v>
+        <v>-0.2448</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.99</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0958</v>
+        <v>-0.0594</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.5984</v>
+        <v>-2.8512</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2185</v>
+        <v>-0.1715</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.488</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2537</v>
+        <v>-0.2046</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.1776</v>
+        <v>-9.8208</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.47</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7565</v>
+        <v>0.9438</v>
       </c>
       <c r="J222" t="n">
-        <v>18.9125</v>
+        <v>23.595</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.58</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1963</v>
+        <v>-0.126</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.9075</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.5178</v>
+        <v>-0.3365</v>
       </c>
       <c r="J225" t="n">
-        <v>-12.945</v>
+        <v>-8.4125</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.59</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6459</v>
+        <v>-0.4298</v>
       </c>
       <c r="J226" t="n">
-        <v>-16.1475</v>
+        <v>-10.745</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.33</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8898</v>
+        <v>0.8794</v>
       </c>
       <c r="J227" t="n">
-        <v>22.245</v>
+        <v>21.985</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.21</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6016</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>15.04</v>
+        <v>14.8575</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.11</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2959</v>
+        <v>0.3419</v>
       </c>
       <c r="J229" t="n">
-        <v>7.3975</v>
+        <v>8.547499999999999</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.06</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1405</v>
+        <v>0.1968</v>
       </c>
       <c r="J230" t="n">
-        <v>3.5125</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.03</v>
       </c>
       <c r="I231" t="n">
-        <v>0.0375</v>
+        <v>0.0975</v>
       </c>
       <c r="J231" t="n">
-        <v>0.9375</v>
+        <v>2.4375</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.18</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3751</v>
+        <v>0.4214</v>
       </c>
       <c r="J232" t="n">
-        <v>10.1277</v>
+        <v>11.3778</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.14</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3147</v>
+        <v>0.3439</v>
       </c>
       <c r="J233" t="n">
-        <v>8.4969</v>
+        <v>9.285299999999999</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.9</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2063</v>
+        <v>-0.128</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.5701</v>
+        <v>-3.456</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.82</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3386</v>
+        <v>-0.2119</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.142200000000001</v>
+        <v>-5.7213</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.67</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5483</v>
+        <v>-0.3578</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.8041</v>
+        <v>-9.660600000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.34</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9122</v>
+        <v>0.9023</v>
       </c>
       <c r="J237" t="n">
-        <v>24.6294</v>
+        <v>24.3621</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8898</v>
+        <v>0.8794</v>
       </c>
       <c r="J238" t="n">
-        <v>24.0246</v>
+        <v>23.7438</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.23</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6529</v>
+        <v>0.6429</v>
       </c>
       <c r="J239" t="n">
-        <v>17.6283</v>
+        <v>17.3583</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.21</v>
       </c>
       <c r="I240" t="n">
-        <v>0.6016</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>16.2432</v>
+        <v>16.0461</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.63</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.0933</v>
+        <v>-1.0804</v>
       </c>
       <c r="J241" t="n">
-        <v>-29.5191</v>
+        <v>-29.1708</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.22</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4073</v>
+        <v>0.4707</v>
       </c>
       <c r="J242" t="n">
-        <v>12.219</v>
+        <v>14.121</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.18</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3495</v>
+        <v>0.3975</v>
       </c>
       <c r="J243" t="n">
-        <v>10.485</v>
+        <v>11.925</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.03</v>
       </c>
       <c r="I244" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="J244" t="n">
-        <v>2.538</v>
+        <v>2.688</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1604</v>
+        <v>-0.0896</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.812</v>
+        <v>-2.688</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.7</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5228</v>
+        <v>-0.3378</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.684</v>
+        <v>-10.134</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.42</v>
       </c>
       <c r="I247" t="n">
-        <v>1.135</v>
+        <v>1.077</v>
       </c>
       <c r="J247" t="n">
-        <v>34.05</v>
+        <v>32.31</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.11</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3887</v>
+        <v>0.3602</v>
       </c>
       <c r="J248" t="n">
-        <v>11.661</v>
+        <v>10.806</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0528</v>
+        <v>-0.0112</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.584</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3332</v>
+        <v>-0.2749</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.996</v>
+        <v>-8.247</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6629</v>
+        <v>-0.6109</v>
       </c>
       <c r="J251" t="n">
-        <v>-19.887</v>
+        <v>-18.327</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4411/event_4411_evp_summary.xlsx
+++ b/database/event/4411/event_4411_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.389699999999999</v>
+        <v>8.533200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3602</v>
+        <v>2.4006</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1495</v>
+        <v>3.2603</v>
       </c>
       <c r="E2" t="n">
-        <v>8.389699999999999</v>
+        <v>8.533200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1436</v>
+        <v>3.0207</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2461</v>
+        <v>5.5124</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5899</v>
+        <v>5.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9065</v>
+        <v>2.739</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2461</v>
+        <v>5.5124</v>
       </c>
       <c r="K2" t="n">
         <v>157</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1526</v>
+        <v>8.2514</v>
       </c>
       <c r="N2" t="n">
         <v>259</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8193</v>
+        <v>5.8041</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6371</v>
+        <v>1.6328</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9891</v>
+        <v>2.0179</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8193</v>
+        <v>5.8041</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8805</v>
+        <v>2.7829</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9388</v>
+        <v>3.0212</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6627</v>
+        <v>4.2877</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4244</v>
+        <v>2.3153</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9388</v>
+        <v>3.0212</v>
       </c>
       <c r="K3" t="n">
         <v>157</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3632</v>
+        <v>5.3365</v>
       </c>
       <c r="N3" t="n">
         <v>259</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9743</v>
+        <v>4.9516</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3994</v>
+        <v>1.393</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6076</v>
+        <v>1.6299</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9743</v>
+        <v>4.9516</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5084</v>
+        <v>2.4043</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4659</v>
+        <v>2.5473</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3518</v>
+        <v>3.0384</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7428</v>
+        <v>1.6407</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4659</v>
+        <v>2.5473</v>
       </c>
       <c r="K4" t="n">
         <v>157</v>
@@ -621,7 +621,7 @@
         <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2087</v>
+        <v>4.188</v>
       </c>
       <c r="N4" t="n">
         <v>259</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6172</v>
+        <v>3.61</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0176</v>
+        <v>1.0156</v>
       </c>
       <c r="D5" t="n">
-        <v>0.995</v>
+        <v>1.0191</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6172</v>
+        <v>3.61</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9733</v>
+        <v>2.8902</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6439</v>
+        <v>0.7198</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9897</v>
+        <v>4.6417</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5944</v>
+        <v>2.5065</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6439</v>
+        <v>0.7198</v>
       </c>
       <c r="K5" t="n">
         <v>127</v>
@@ -667,7 +667,7 @@
         <v>69</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2383</v>
+        <v>3.2263</v>
       </c>
       <c r="N5" t="n">
         <v>196</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5835</v>
+        <v>3.5915</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0081</v>
+        <v>1.0104</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9798</v>
+        <v>1.0107</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5835</v>
+        <v>3.5915</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8829</v>
+        <v>2.8107</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7006</v>
+        <v>0.7808</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6712</v>
+        <v>4.3793</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4288</v>
+        <v>2.3648</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7006</v>
+        <v>0.7808</v>
       </c>
       <c r="K6" t="n">
         <v>81</v>
@@ -713,7 +713,7 @@
         <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1294</v>
+        <v>3.1456</v>
       </c>
       <c r="N6" t="n">
         <v>138</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4883</v>
+        <v>3.1867</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9813</v>
+        <v>0.8965</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9368</v>
+        <v>0.8264</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4883</v>
+        <v>3.1867</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4883</v>
+        <v>3.1867</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>4.2498</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>4.2498</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3</v>
+        <v>4.2498</v>
       </c>
       <c r="N7" t="n">
         <v>156</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0723</v>
+        <v>3.032</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8643</v>
+        <v>0.853</v>
       </c>
       <c r="D8" t="n">
-        <v>0.749</v>
+        <v>0.756</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0723</v>
+        <v>3.032</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1648</v>
+        <v>2.0206</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9075</v>
+        <v>1.0114</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1648</v>
+        <v>2.0206</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1256</v>
+        <v>1.0911</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9075</v>
+        <v>1.0114</v>
       </c>
       <c r="K8" t="n">
         <v>127</v>
@@ -805,7 +805,7 @@
         <v>69</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0331</v>
+        <v>2.1025</v>
       </c>
       <c r="N8" t="n">
         <v>196</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9914</v>
+        <v>2.9148</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8415</v>
+        <v>0.82</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7125</v>
+        <v>0.7027</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9914</v>
+        <v>2.9148</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8665</v>
+        <v>2.7701</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1249</v>
+        <v>0.1447</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6133</v>
+        <v>4.2454</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3987</v>
+        <v>2.2925</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1249</v>
+        <v>0.1447</v>
       </c>
       <c r="K9" t="n">
         <v>81</v>
@@ -851,7 +851,7 @@
         <v>57</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5236</v>
+        <v>2.4372</v>
       </c>
       <c r="N9" t="n">
         <v>138</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8012</v>
+        <v>2.6821</v>
       </c>
       <c r="C10" t="n">
-        <v>0.788</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6266</v>
+        <v>0.5967</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8012</v>
+        <v>2.6821</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8629</v>
+        <v>2.7528</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0617</v>
+        <v>-0.0707</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6008</v>
+        <v>4.1882</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3922</v>
+        <v>2.2616</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0617</v>
+        <v>-0.0707</v>
       </c>
       <c r="K10" t="n">
         <v>81</v>
@@ -897,7 +897,7 @@
         <v>57</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3305</v>
+        <v>2.1909</v>
       </c>
       <c r="N10" t="n">
         <v>138</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6805</v>
+        <v>2.4303</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7541</v>
+        <v>0.6837</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.4821</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6805</v>
+        <v>2.4303</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6805</v>
+        <v>2.4303</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6805</v>
+        <v>2.5942</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6805</v>
+        <v>2.5942</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6805</v>
+        <v>2.5942</v>
       </c>
       <c r="N11" t="n">
         <v>153</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5567</v>
+        <v>2.3869</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6715</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5162</v>
+        <v>0.4624</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5567</v>
+        <v>2.3869</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5567</v>
+        <v>2.3869</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5567</v>
+        <v>2.4992</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5567</v>
+        <v>2.4992</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5567</v>
+        <v>2.4992</v>
       </c>
       <c r="N12" t="n">
         <v>156</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4887</v>
+        <v>2.3068</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.649</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4855</v>
+        <v>0.4259</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4887</v>
+        <v>2.3068</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4887</v>
+        <v>2.3068</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4887</v>
+        <v>2.324</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4887</v>
+        <v>2.324</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4887</v>
+        <v>2.324</v>
       </c>
       <c r="N13" t="n">
         <v>153</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.43</v>
+        <v>2.3041</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6836</v>
+        <v>0.6482</v>
       </c>
       <c r="D14" t="n">
-        <v>0.459</v>
+        <v>0.4247</v>
       </c>
       <c r="E14" t="n">
-        <v>2.43</v>
+        <v>2.3041</v>
       </c>
       <c r="F14" t="n">
-        <v>2.185</v>
+        <v>1.9876</v>
       </c>
       <c r="G14" t="n">
-        <v>0.245</v>
+        <v>0.3165</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2123</v>
+        <v>1.9876</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1503</v>
+        <v>1.0733</v>
       </c>
       <c r="J14" t="n">
-        <v>0.245</v>
+        <v>0.3165</v>
       </c>
       <c r="K14" t="n">
         <v>167</v>
@@ -1081,7 +1081,7 @@
         <v>114</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3953</v>
+        <v>1.3898</v>
       </c>
       <c r="N14" t="n">
         <v>281</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3393</v>
+        <v>2.2567</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6581</v>
+        <v>0.6349</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4181</v>
+        <v>0.4031</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3393</v>
+        <v>2.2567</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3393</v>
+        <v>2.2567</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3393</v>
+        <v>2.2567</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3393</v>
+        <v>2.2567</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3393</v>
+        <v>2.2567</v>
       </c>
       <c r="N15" t="n">
         <v>156</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.327</v>
+        <v>2.2203</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6546</v>
+        <v>0.6246</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4125</v>
+        <v>0.3865</v>
       </c>
       <c r="E16" t="n">
-        <v>2.327</v>
+        <v>2.2203</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3168</v>
+        <v>2.2172</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0102</v>
+        <v>0.0031</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6768</v>
+        <v>2.4213</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3918</v>
+        <v>1.3075</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0102</v>
+        <v>0.0031</v>
       </c>
       <c r="K16" t="n">
         <v>157</v>
@@ -1173,7 +1173,7 @@
         <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>1.402</v>
+        <v>1.3106</v>
       </c>
       <c r="N16" t="n">
         <v>259</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2467</v>
+        <v>2.183</v>
       </c>
       <c r="C17" t="n">
-        <v>0.632</v>
+        <v>0.6141</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3763</v>
+        <v>0.3695</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2467</v>
+        <v>2.183</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2467</v>
+        <v>2.183</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2467</v>
+        <v>2.183</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2467</v>
+        <v>2.183</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2467</v>
+        <v>2.183</v>
       </c>
       <c r="N17" t="n">
         <v>156</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2232</v>
+        <v>2.1119</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6254</v>
+        <v>0.5941</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3656</v>
+        <v>0.3372</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2232</v>
+        <v>2.1119</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5741</v>
+        <v>2.4808</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3509</v>
+        <v>-0.3689</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5832</v>
+        <v>3.291</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8631</v>
+        <v>1.7771</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3509</v>
+        <v>-0.3689</v>
       </c>
       <c r="K18" t="n">
         <v>127</v>
@@ -1265,7 +1265,7 @@
         <v>69</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5122</v>
+        <v>1.4082</v>
       </c>
       <c r="N18" t="n">
         <v>196</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8473</v>
+        <v>1.7494</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.4921</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1959</v>
+        <v>0.1722</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8473</v>
+        <v>1.7494</v>
       </c>
       <c r="F19" t="n">
-        <v>1.984</v>
+        <v>1.9043</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1367</v>
+        <v>-0.1549</v>
       </c>
       <c r="H19" t="n">
-        <v>1.984</v>
+        <v>1.9043</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0316</v>
+        <v>1.0283</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1367</v>
+        <v>-0.1549</v>
       </c>
       <c r="K19" t="n">
         <v>81</v>
@@ -1311,7 +1311,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8949</v>
+        <v>0.8734</v>
       </c>
       <c r="N19" t="n">
         <v>138</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5898</v>
+        <v>1.529</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4472</v>
+        <v>0.4301</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0718</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5898</v>
+        <v>1.529</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5898</v>
+        <v>1.529</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5898</v>
+        <v>1.529</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5898</v>
+        <v>1.529</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5898</v>
+        <v>1.529</v>
       </c>
       <c r="N20" t="n">
         <v>123</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4865</v>
+        <v>1.4386</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4182</v>
+        <v>0.4047</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0331</v>
+        <v>0.0307</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4865</v>
+        <v>1.4386</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4865</v>
+        <v>1.4386</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4865</v>
+        <v>1.4386</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4865</v>
+        <v>1.4386</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4865</v>
+        <v>1.4386</v>
       </c>
       <c r="N21" t="n">
         <v>153</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9791</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2754</v>
+        <v>0.2755</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.196</v>
+        <v>-0.1784</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9791</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.848</v>
+        <v>0.8454</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1311</v>
+        <v>0.1339</v>
       </c>
       <c r="H22" t="n">
-        <v>0.848</v>
+        <v>0.8454</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4409</v>
+        <v>0.4565</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1311</v>
+        <v>0.1339</v>
       </c>
       <c r="K22" t="n">
         <v>127</v>
@@ -1449,7 +1449,7 @@
         <v>69</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.5904</v>
       </c>
       <c r="N22" t="n">
         <v>196</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3173</v>
+        <v>0.3254</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0893</v>
+        <v>0.0915</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4948</v>
+        <v>-0.4761</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3173</v>
+        <v>0.3254</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0371</v>
+        <v>-0.062</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3544</v>
+        <v>0.3874</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0371</v>
+        <v>-0.062</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0193</v>
+        <v>-0.0335</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3544</v>
+        <v>0.3874</v>
       </c>
       <c r="K23" t="n">
         <v>127</v>
@@ -1495,7 +1495,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3351</v>
+        <v>0.3539</v>
       </c>
       <c r="N23" t="n">
         <v>196</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2474</v>
+        <v>0.2349</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0696</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5263</v>
+        <v>-0.5173</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2474</v>
+        <v>0.2349</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2474</v>
+        <v>0.2349</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2474</v>
+        <v>0.2349</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2474</v>
+        <v>0.2349</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2474</v>
+        <v>0.2349</v>
       </c>
       <c r="N24" t="n">
         <v>123</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2402</v>
+        <v>0.1924</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0541</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5296</v>
+        <v>-0.5366</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2402</v>
+        <v>0.1924</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2402</v>
+        <v>0.1924</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2402</v>
+        <v>0.1924</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2402</v>
+        <v>0.1924</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2402</v>
+        <v>0.1924</v>
       </c>
       <c r="N25" t="n">
         <v>70</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0523</v>
+        <v>0.0703</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0147</v>
+        <v>0.0198</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0523</v>
+        <v>0.0703</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0523</v>
+        <v>0.0703</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0523</v>
+        <v>0.0703</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0523</v>
+        <v>0.0703</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0523</v>
+        <v>0.0703</v>
       </c>
       <c r="N26" t="n">
         <v>156</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0273</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0023</v>
+        <v>0.0077</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6343</v>
+        <v>-0.6118</v>
       </c>
       <c r="E27" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0273</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1198</v>
+        <v>0.1181</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1116</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1198</v>
+        <v>0.1181</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0623</v>
+        <v>0.0638</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1116</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>167</v>
@@ -1679,7 +1679,7 @@
         <v>114</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0493</v>
+        <v>-0.02700000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>281</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0582</v>
+        <v>-0.1198</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0164</v>
+        <v>-0.0337</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6643</v>
+        <v>-0.6787</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0582</v>
+        <v>-0.1198</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4651</v>
+        <v>-0.1198</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.5233</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.4651</v>
+        <v>-0.1198</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7618</v>
+        <v>-0.1198</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.5233</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="L28" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.7615000000000001</v>
+        <v>-0.1198</v>
       </c>
       <c r="N28" t="n">
-        <v>281</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1049</v>
+        <v>-0.2861</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0295</v>
+        <v>-0.0805</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6854</v>
+        <v>-0.7544</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1049</v>
+        <v>-0.2861</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1049</v>
+        <v>1.2574</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-1.5435</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1049</v>
+        <v>1.2574</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1049</v>
+        <v>0.679</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-1.5435</v>
       </c>
       <c r="K29" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1049</v>
+        <v>-0.8645</v>
       </c>
       <c r="N29" t="n">
-        <v>123</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2663</v>
+        <v>-0.3126</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7582</v>
+        <v>-0.7665</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2663</v>
+        <v>-0.3126</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2663</v>
+        <v>-0.3126</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2663</v>
+        <v>-0.3126</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2663</v>
+        <v>-0.3126</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2663</v>
+        <v>-0.3126</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4824</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1357</v>
+        <v>-0.1513</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8558</v>
+        <v>-0.869</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4824</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4824</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4824</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4824</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4824</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>153</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6353</v>
+        <v>-0.6592</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1787</v>
+        <v>-0.1854</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9248</v>
+        <v>-0.9243</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6353</v>
+        <v>-0.6592</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6353</v>
+        <v>-0.6592</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6353</v>
+        <v>-0.6592</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6353</v>
+        <v>-0.6592</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6353</v>
+        <v>-0.6592</v>
       </c>
       <c r="N32" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6368</v>
+        <v>-0.6987</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1791</v>
+        <v>-0.1966</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9255</v>
+        <v>-0.9423</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6368</v>
+        <v>-0.6987</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6368</v>
+        <v>-0.6987</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6368</v>
+        <v>-0.6987</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6368</v>
+        <v>-0.6987</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6368</v>
+        <v>-0.6987</v>
       </c>
       <c r="N33" t="n">
-        <v>123</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6746</v>
+        <v>-0.7005</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1898</v>
+        <v>-0.1971</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9426</v>
+        <v>-0.9431</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6746</v>
+        <v>-0.7005</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6746</v>
+        <v>-0.7005</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6746</v>
+        <v>-0.7005</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6746</v>
+        <v>-0.7005</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6746</v>
+        <v>-0.7005</v>
       </c>
       <c r="N34" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7721</v>
+        <v>-0.7081</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2172</v>
+        <v>-0.1992</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9866</v>
+        <v>-0.9465</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7721</v>
+        <v>-0.7081</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7721</v>
+        <v>-0.7081</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7721</v>
+        <v>-0.7081</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7721</v>
+        <v>-0.7081</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7721</v>
+        <v>-0.7081</v>
       </c>
       <c r="N35" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1006</v>
+        <v>-1.1459</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3096</v>
+        <v>-0.3224</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1349</v>
+        <v>-1.1458</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1006</v>
+        <v>-1.1459</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1006</v>
+        <v>-1.1459</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1006</v>
+        <v>-1.1459</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1006</v>
+        <v>-1.1459</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1006</v>
+        <v>-1.1459</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2895</v>
+        <v>-1.3299</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3628</v>
+        <v>-0.3741</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2202</v>
+        <v>-1.2296</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2895</v>
+        <v>-1.3299</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2895</v>
+        <v>-1.3299</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2895</v>
+        <v>-1.3299</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2895</v>
+        <v>-1.3299</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2895</v>
+        <v>-1.3299</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.6024</v>
+        <v>-2.4948</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7321</v>
+        <v>-0.7018</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.8129</v>
+        <v>-1.7599</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.6024</v>
+        <v>-2.4948</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.3258</v>
+        <v>-2.2836</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2766</v>
+        <v>-0.2112</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.3258</v>
+        <v>-2.2836</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2093</v>
+        <v>-1.2331</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2766</v>
+        <v>-0.2112</v>
       </c>
       <c r="K38" t="n">
         <v>167</v>
@@ -2185,7 +2185,7 @@
         <v>114</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4859</v>
+        <v>-1.4443</v>
       </c>
       <c r="N38" t="n">
         <v>281</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ableJ</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.9339</v>
+        <v>-2.5611</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8254</v>
+        <v>-0.7205</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.9625</v>
+        <v>-1.7901</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.9339</v>
+        <v>-2.5611</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3128</v>
+        <v>-2.2226</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.6211</v>
+        <v>-0.3385</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3128</v>
+        <v>-2.2226</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6826</v>
+        <v>-1.2002</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.6211</v>
+        <v>-0.3385</v>
       </c>
       <c r="K39" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L39" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.3037</v>
+        <v>-1.5387</v>
       </c>
       <c r="N39" t="n">
-        <v>281</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>ableJ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.007</v>
+        <v>-3.0541</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8459</v>
+        <v>-0.8592</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.9955</v>
+        <v>-2.0145</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.007</v>
+        <v>-3.0541</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.4618</v>
+        <v>-1.3967</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5452</v>
+        <v>-1.6574</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.4618</v>
+        <v>-1.3967</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.28</v>
+        <v>-0.7542</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5452</v>
+        <v>-1.6574</v>
       </c>
       <c r="K40" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="L40" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8252</v>
+        <v>-2.4116</v>
       </c>
       <c r="N40" t="n">
-        <v>259</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.4275</v>
+        <v>-3.9919</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.2456</v>
+        <v>-1.123</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.6368</v>
+        <v>-2.4414</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.4275</v>
+        <v>-3.9919</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.0448</v>
+        <v>-3.583</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.3827</v>
+        <v>-0.4089</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.0448</v>
+        <v>-3.583</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.1031</v>
+        <v>-1.9348</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3827</v>
+        <v>-0.4089</v>
       </c>
       <c r="K41" t="n">
         <v>81</v>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4858</v>
+        <v>-2.3437</v>
       </c>
       <c r="N41" t="n">
         <v>138</v>
@@ -2429,10 +2429,10 @@
         <v>1.03</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1363</v>
+        <v>0.1323</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4075</v>
+        <v>3.3075</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.99</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0004</v>
+        <v>-0.0097</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.01</v>
+        <v>-0.2425</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.22</v>
+        <v>-0.2376</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.5</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.75</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2687</v>
+        <v>-0.2856</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.7175</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.65</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.364</v>
+        <v>-0.378</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.1</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.56</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2015</v>
+        <v>1.2306</v>
       </c>
       <c r="J7" t="n">
-        <v>30.0375</v>
+        <v>30.765</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.45</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0632</v>
+        <v>1.0296</v>
       </c>
       <c r="J8" t="n">
-        <v>26.58</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.778</v>
+        <v>0.7423</v>
       </c>
       <c r="J9" t="n">
-        <v>19.45</v>
+        <v>18.5575</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.27</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7113</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>17.7825</v>
+        <v>17.075</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.75</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8163</v>
+        <v>-0.7477</v>
       </c>
       <c r="J11" t="n">
-        <v>-20.4075</v>
+        <v>-18.6925</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.8</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1735</v>
+        <v>-0.2016</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.47</v>
+        <v>-4.032</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2283</v>
+        <v>-0.2544</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.566</v>
+        <v>-5.088</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.57</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4011</v>
+        <v>-0.4198</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.022</v>
+        <v>-8.396000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.47</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4944</v>
+        <v>-0.5074</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.888</v>
+        <v>-10.148</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.44</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5229</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.458</v>
+        <v>-10.676</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>2.14</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8266</v>
+        <v>1.8453</v>
       </c>
       <c r="J17" t="n">
-        <v>36.532</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.56</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1673</v>
+        <v>1.1901</v>
       </c>
       <c r="J18" t="n">
-        <v>23.346</v>
+        <v>23.802</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7883</v>
+        <v>0.7582</v>
       </c>
       <c r="J19" t="n">
-        <v>15.766</v>
+        <v>15.164</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.18</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4565</v>
+        <v>0.4632</v>
       </c>
       <c r="J20" t="n">
-        <v>9.130000000000001</v>
+        <v>9.263999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.12</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2989</v>
+        <v>0.3201</v>
       </c>
       <c r="J21" t="n">
-        <v>5.978</v>
+        <v>6.402</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7943</v>
+        <v>0.8875</v>
       </c>
       <c r="J22" t="n">
-        <v>27.0062</v>
+        <v>30.175</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3855</v>
+        <v>0.4201</v>
       </c>
       <c r="J23" t="n">
-        <v>13.107</v>
+        <v>14.2834</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1064</v>
+        <v>-0.1165</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.6176</v>
+        <v>-3.961</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.79</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2557</v>
+        <v>-0.2676</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.6938</v>
+        <v>-9.0984</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2852</v>
+        <v>-0.2966</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.6968</v>
+        <v>-10.0844</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1527</v>
+        <v>1.2582</v>
       </c>
       <c r="J27" t="n">
-        <v>39.1918</v>
+        <v>42.7788</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6232</v>
+        <v>0.6903</v>
       </c>
       <c r="J28" t="n">
-        <v>21.1888</v>
+        <v>23.4702</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.27</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5682</v>
+        <v>0.6296</v>
       </c>
       <c r="J29" t="n">
-        <v>19.3188</v>
+        <v>21.4064</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6424</v>
+        <v>-0.5975</v>
       </c>
       <c r="J30" t="n">
-        <v>-21.8416</v>
+        <v>-20.315</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7953</v>
+        <v>-0.7328</v>
       </c>
       <c r="J31" t="n">
-        <v>-27.0402</v>
+        <v>-24.9152</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.08</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2235</v>
+        <v>0.2259</v>
       </c>
       <c r="J32" t="n">
-        <v>5.1405</v>
+        <v>5.1957</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.98</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0303</v>
+        <v>-0.0384</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6969</v>
+        <v>-0.8832</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.93</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1067</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.1551</v>
+        <v>-2.4541</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.127</v>
+        <v>-0.1413</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.921</v>
+        <v>-3.2499</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2606</v>
+        <v>-0.2754</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.9938</v>
+        <v>-6.3342</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.74</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1508</v>
+        <v>1.2605</v>
       </c>
       <c r="J37" t="n">
-        <v>26.4684</v>
+        <v>28.9915</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.46</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8043</v>
+        <v>0.8911</v>
       </c>
       <c r="J38" t="n">
-        <v>18.4989</v>
+        <v>20.4953</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.31</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6099</v>
+        <v>0.6788</v>
       </c>
       <c r="J39" t="n">
-        <v>14.0277</v>
+        <v>15.6124</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.91</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3878</v>
+        <v>-0.3627</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.9194</v>
+        <v>-8.3421</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5293</v>
+        <v>-0.492</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.1739</v>
+        <v>-11.316</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4709</v>
+        <v>0.5238</v>
       </c>
       <c r="J42" t="n">
-        <v>12.7143</v>
+        <v>14.1426</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3877</v>
+        <v>0.4225</v>
       </c>
       <c r="J43" t="n">
-        <v>10.4679</v>
+        <v>11.4075</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1097</v>
+        <v>0.1201</v>
       </c>
       <c r="J44" t="n">
-        <v>2.9619</v>
+        <v>3.2427</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.093</v>
+        <v>-0.1027</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.511</v>
+        <v>-2.7729</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.77</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.274</v>
+        <v>-0.2858</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.398</v>
+        <v>-7.7166</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8706</v>
+        <v>0.9497</v>
       </c>
       <c r="J47" t="n">
-        <v>23.5062</v>
+        <v>25.6419</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.21</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5137</v>
+        <v>0.5614</v>
       </c>
       <c r="J48" t="n">
-        <v>13.8699</v>
+        <v>15.1578</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.82</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5446</v>
       </c>
       <c r="J49" t="n">
-        <v>-15.5007</v>
+        <v>-14.7042</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6004</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-16.2108</v>
+        <v>-15.336</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.79</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6525</v>
+        <v>-0.6142</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.6175</v>
+        <v>-16.5834</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5342</v>
+        <v>0.5997</v>
       </c>
       <c r="J52" t="n">
-        <v>22.4364</v>
+        <v>25.1874</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.26</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4366</v>
+        <v>0.4876</v>
       </c>
       <c r="J53" t="n">
-        <v>18.3372</v>
+        <v>20.4792</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2241</v>
+        <v>0.2366</v>
       </c>
       <c r="J54" t="n">
-        <v>9.4122</v>
+        <v>9.937200000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0333</v>
+        <v>-0.0351</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.3986</v>
+        <v>-1.4742</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0769</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.2298</v>
+        <v>-3.4902</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.44</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8613</v>
+        <v>0.9364</v>
       </c>
       <c r="J57" t="n">
-        <v>36.1746</v>
+        <v>39.3288</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.03</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1378</v>
+        <v>0.1408</v>
       </c>
       <c r="J58" t="n">
-        <v>5.7876</v>
+        <v>5.9136</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.83</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5336</v>
+        <v>-0.5111</v>
       </c>
       <c r="J59" t="n">
-        <v>-22.4112</v>
+        <v>-21.4662</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.82</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5601</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>-23.5242</v>
+        <v>-22.4616</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7659</v>
+        <v>-0.7164</v>
       </c>
       <c r="J61" t="n">
-        <v>-32.1678</v>
+        <v>-30.0888</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.42</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0379</v>
+        <v>0.9856</v>
       </c>
       <c r="J62" t="n">
-        <v>30.0991</v>
+        <v>28.5824</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9712</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>28.1648</v>
+        <v>26.4712</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.31</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8182</v>
+        <v>0.7743</v>
       </c>
       <c r="J64" t="n">
-        <v>23.7278</v>
+        <v>22.4547</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.13</v>
       </c>
       <c r="I65" t="n">
-        <v>0.386</v>
+        <v>0.3867</v>
       </c>
       <c r="J65" t="n">
-        <v>11.194</v>
+        <v>11.2143</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.85</v>
+        <v>-0.7799</v>
       </c>
       <c r="J66" t="n">
-        <v>-24.65</v>
+        <v>-22.6171</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.19</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4309</v>
+        <v>0.4244</v>
       </c>
       <c r="J67" t="n">
-        <v>12.4961</v>
+        <v>12.3076</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.96</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0605</v>
+        <v>-0.0704</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.7545</v>
+        <v>-2.0416</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0968</v>
+        <v>-0.109</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.8072</v>
+        <v>-3.161</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1307</v>
+        <v>-0.1442</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.7903</v>
+        <v>-4.1818</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1738</v>
+        <v>-0.188</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.0402</v>
+        <v>-5.452</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1585</v>
+        <v>1.1265</v>
       </c>
       <c r="J72" t="n">
-        <v>27.804</v>
+        <v>27.036</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.9479</v>
       </c>
       <c r="J73" t="n">
-        <v>24</v>
+        <v>22.7496</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.32</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8171</v>
+        <v>0.7779</v>
       </c>
       <c r="J74" t="n">
-        <v>19.6104</v>
+        <v>18.6696</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.26</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6604</v>
       </c>
       <c r="J75" t="n">
-        <v>16.44</v>
+        <v>15.8496</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.95</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2731</v>
+        <v>-0.2532</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.5544</v>
+        <v>-6.0768</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.11</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2967</v>
+        <v>0.2939</v>
       </c>
       <c r="J77" t="n">
-        <v>7.1208</v>
+        <v>7.0536</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0895</v>
       </c>
       <c r="J78" t="n">
-        <v>2.1216</v>
+        <v>2.148</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0589</v>
+        <v>0.0586</v>
       </c>
       <c r="J79" t="n">
-        <v>1.4136</v>
+        <v>1.4064</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0926</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.9128</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.44</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5638</v>
+        <v>-0.5661</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.5312</v>
+        <v>-13.5864</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.16</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3269</v>
+        <v>0.3215</v>
       </c>
       <c r="J82" t="n">
-        <v>9.1532</v>
+        <v>9.002000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1442</v>
+        <v>0.1438</v>
       </c>
       <c r="J83" t="n">
-        <v>4.0376</v>
+        <v>4.0264</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.86</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1607</v>
+        <v>-0.1781</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.4996</v>
+        <v>-4.9868</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.71</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3066</v>
+        <v>-0.3227</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.5848</v>
+        <v>-9.035600000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.42</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5752</v>
+        <v>-0.5777</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.1056</v>
+        <v>-16.1756</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5893</v>
+        <v>0.5915</v>
       </c>
       <c r="J87" t="n">
-        <v>16.5004</v>
+        <v>16.562</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.24</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3346</v>
+        <v>0.3496</v>
       </c>
       <c r="J88" t="n">
-        <v>9.3688</v>
+        <v>9.7888</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2735</v>
+        <v>0.2901</v>
       </c>
       <c r="J89" t="n">
-        <v>7.658</v>
+        <v>8.1228</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0142</v>
+        <v>-0.0109</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.3976</v>
+        <v>-0.3052</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1727</v>
+        <v>-0.1822</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.8356</v>
+        <v>-5.1016</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6452</v>
+        <v>0.6091</v>
       </c>
       <c r="J92" t="n">
-        <v>16.7752</v>
+        <v>15.8366</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.013</v>
+        <v>-0.0078</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0944</v>
+        <v>-0.1</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.4544</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2301</v>
+        <v>-0.2312</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.9826</v>
+        <v>-6.0112</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.89</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3787</v>
+        <v>-0.369</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.8462</v>
+        <v>-9.593999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.49</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9371</v>
+        <v>0.8855</v>
       </c>
       <c r="J97" t="n">
-        <v>24.3646</v>
+        <v>23.023</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2677</v>
+        <v>0.2726</v>
       </c>
       <c r="J98" t="n">
-        <v>6.9602</v>
+        <v>7.0876</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0667</v>
+        <v>0.0738</v>
       </c>
       <c r="J99" t="n">
-        <v>1.7342</v>
+        <v>1.9188</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1557</v>
+        <v>-0.169</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.0482</v>
+        <v>-4.394</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.48</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.5394</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.9568</v>
+        <v>-14.0244</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.633</v>
+        <v>0.6006</v>
       </c>
       <c r="J102" t="n">
-        <v>18.357</v>
+        <v>17.4174</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.09</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3098</v>
+        <v>0.3082</v>
       </c>
       <c r="J103" t="n">
-        <v>8.9842</v>
+        <v>8.937799999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.124</v>
+        <v>0.1314</v>
       </c>
       <c r="J104" t="n">
-        <v>3.596</v>
+        <v>3.8106</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2377</v>
+        <v>-0.2364</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.8933</v>
+        <v>-6.8556</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.89</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3868</v>
+        <v>-0.3747</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.2172</v>
+        <v>-10.8663</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.4</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7642</v>
+        <v>0.7338</v>
       </c>
       <c r="J107" t="n">
-        <v>22.1618</v>
+        <v>21.2802</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6476</v>
+        <v>0.6287</v>
       </c>
       <c r="J108" t="n">
-        <v>18.7804</v>
+        <v>18.2323</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.92</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1179</v>
+        <v>-0.1285</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.4191</v>
+        <v>-3.7265</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2049</v>
+        <v>-0.217</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.9421</v>
+        <v>-6.293</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2456</v>
+        <v>-0.2575</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.1224</v>
+        <v>-7.4675</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.82</v>
       </c>
       <c r="I112" t="n">
-        <v>1.473</v>
+        <v>1.4666</v>
       </c>
       <c r="J112" t="n">
-        <v>29.46</v>
+        <v>29.332</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.6</v>
       </c>
       <c r="I113" t="n">
-        <v>1.2175</v>
+        <v>1.195</v>
       </c>
       <c r="J113" t="n">
-        <v>24.35</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.33</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8149</v>
+        <v>0.7808</v>
       </c>
       <c r="J114" t="n">
-        <v>16.298</v>
+        <v>15.616</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.3</v>
       </c>
       <c r="I115" t="n">
-        <v>0.7477</v>
+        <v>0.7216</v>
       </c>
       <c r="J115" t="n">
-        <v>14.954</v>
+        <v>14.432</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.16</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4099</v>
+        <v>0.4202</v>
       </c>
       <c r="J116" t="n">
-        <v>8.198</v>
+        <v>8.404</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.89</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0795</v>
+        <v>-0.1071</v>
       </c>
       <c r="J117" t="n">
-        <v>-1.59</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.63</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3521</v>
+        <v>-0.3721</v>
       </c>
       <c r="J118" t="n">
-        <v>-7.042</v>
+        <v>-7.442</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.63</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3521</v>
+        <v>-0.3721</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.042</v>
+        <v>-7.442</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.54</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4345</v>
+        <v>-0.4505</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.69</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.5</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4721</v>
+        <v>-0.4857</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.442</v>
+        <v>-9.714</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.34</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5308</v>
+        <v>0.5212</v>
       </c>
       <c r="J122" t="n">
-        <v>13.27</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0529</v>
+        <v>0.0592</v>
       </c>
       <c r="J123" t="n">
-        <v>1.3225</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0485</v>
+        <v>-0.0571</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.2125</v>
+        <v>-1.4275</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1432</v>
+        <v>-0.1567</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.58</v>
+        <v>-3.9175</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3437</v>
+        <v>-0.3552</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.592499999999999</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.27</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3728</v>
+        <v>0.386</v>
       </c>
       <c r="J127" t="n">
-        <v>9.32</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3245</v>
+        <v>0.3394</v>
       </c>
       <c r="J128" t="n">
-        <v>8.112500000000001</v>
+        <v>8.484999999999999</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2375</v>
+        <v>0.2541</v>
       </c>
       <c r="J129" t="n">
-        <v>5.9375</v>
+        <v>6.3525</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0501</v>
+        <v>0.0629</v>
       </c>
       <c r="J130" t="n">
-        <v>1.2525</v>
+        <v>1.5725</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.01</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0108</v>
+        <v>0.0202</v>
       </c>
       <c r="J131" t="n">
-        <v>0.27</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.4</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0444</v>
+        <v>0.9855</v>
       </c>
       <c r="J132" t="n">
-        <v>31.332</v>
+        <v>29.565</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8164</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="J133" t="n">
-        <v>24.492</v>
+        <v>22.938</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.03</v>
       </c>
       <c r="I134" t="n">
-        <v>0.117</v>
+        <v>0.1267</v>
       </c>
       <c r="J134" t="n">
-        <v>3.51</v>
+        <v>3.801</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0805</v>
+        <v>0.0906</v>
       </c>
       <c r="J135" t="n">
-        <v>2.415</v>
+        <v>2.718</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.1327</v>
+        <v>-1.0297</v>
       </c>
       <c r="J136" t="n">
-        <v>-33.981</v>
+        <v>-30.891</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.43</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8238</v>
+        <v>0.7856</v>
       </c>
       <c r="J137" t="n">
-        <v>24.714</v>
+        <v>23.568</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.14</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3173</v>
+        <v>0.3219</v>
       </c>
       <c r="J138" t="n">
-        <v>9.519</v>
+        <v>9.657</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1151</v>
+        <v>-0.1263</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.453</v>
+        <v>-3.789</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1705</v>
+        <v>-0.183</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.115</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.8</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2427</v>
+        <v>-0.2553</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.281</v>
+        <v>-7.659</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.9</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5469</v>
+        <v>1.5473</v>
       </c>
       <c r="J142" t="n">
-        <v>32.4849</v>
+        <v>32.4933</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.87</v>
       </c>
       <c r="I143" t="n">
-        <v>1.5134</v>
+        <v>1.512</v>
       </c>
       <c r="J143" t="n">
-        <v>31.7814</v>
+        <v>31.752</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.57</v>
       </c>
       <c r="I144" t="n">
-        <v>1.1724</v>
+        <v>1.1486</v>
       </c>
       <c r="J144" t="n">
-        <v>24.6204</v>
+        <v>24.1206</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.29</v>
       </c>
       <c r="I145" t="n">
-        <v>0.7085</v>
+        <v>0.6901</v>
       </c>
       <c r="J145" t="n">
-        <v>14.8785</v>
+        <v>14.4921</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.99</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1742</v>
+        <v>-0.143</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.6582</v>
+        <v>-3.003</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.82</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.1387</v>
+        <v>-0.17</v>
       </c>
       <c r="J147" t="n">
-        <v>-2.9127</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.64</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3325</v>
+        <v>-0.3553</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.9825</v>
+        <v>-7.4613</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.6</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3704</v>
+        <v>-0.3914</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.7784</v>
+        <v>-8.2194</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.49</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4696</v>
+        <v>-0.4852</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.861599999999999</v>
+        <v>-10.1892</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.33</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6231</v>
+        <v>-0.6269</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.0851</v>
+        <v>-13.1649</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.66</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3104</v>
+        <v>1.2901</v>
       </c>
       <c r="J152" t="n">
-        <v>28.8288</v>
+        <v>28.3822</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.39</v>
       </c>
       <c r="I153" t="n">
-        <v>0.9584</v>
+        <v>0.9065</v>
       </c>
       <c r="J153" t="n">
-        <v>21.0848</v>
+        <v>19.943</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.36</v>
       </c>
       <c r="I154" t="n">
-        <v>0.898</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="J154" t="n">
-        <v>19.756</v>
+        <v>18.7066</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3828</v>
+        <v>0.3903</v>
       </c>
       <c r="J155" t="n">
-        <v>8.4216</v>
+        <v>8.586600000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.08</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2151</v>
+        <v>0.2359</v>
       </c>
       <c r="J156" t="n">
-        <v>4.7322</v>
+        <v>5.1898</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4419</v>
+        <v>0.4055</v>
       </c>
       <c r="J157" t="n">
-        <v>9.7218</v>
+        <v>8.920999999999999</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.72</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2777</v>
+        <v>-0.2986</v>
       </c>
       <c r="J158" t="n">
-        <v>-6.1094</v>
+        <v>-6.5692</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.62</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3686</v>
+        <v>-0.3866</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.1092</v>
+        <v>-8.5052</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.52</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4621</v>
+        <v>-0.4749</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.1662</v>
+        <v>-10.4478</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.46</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5183</v>
+        <v>-0.5275</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.4026</v>
+        <v>-11.605</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.416</v>
+        <v>0.4259</v>
       </c>
       <c r="J162" t="n">
-        <v>12.064</v>
+        <v>12.3511</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.29</v>
       </c>
       <c r="I163" t="n">
-        <v>0.404</v>
+        <v>0.4145</v>
       </c>
       <c r="J163" t="n">
-        <v>11.716</v>
+        <v>12.0205</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.08</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1345</v>
+        <v>0.1494</v>
       </c>
       <c r="J164" t="n">
-        <v>3.9005</v>
+        <v>4.3326</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0987</v>
+        <v>-0.1072</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.8623</v>
+        <v>-3.1088</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1562</v>
+        <v>-0.1668</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.5298</v>
+        <v>-4.8372</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.29</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4686</v>
+        <v>0.4628</v>
       </c>
       <c r="J167" t="n">
-        <v>13.5894</v>
+        <v>13.4212</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0551</v>
+        <v>0.0608</v>
       </c>
       <c r="J168" t="n">
-        <v>1.5979</v>
+        <v>1.7632</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1632</v>
+        <v>-0.1773</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.7328</v>
+        <v>-5.1417</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.86</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1738</v>
+        <v>-0.188</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.0402</v>
+        <v>-5.452</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2352</v>
+        <v>-0.2495</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.8208</v>
+        <v>-7.2355</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6686</v>
+        <v>0.6412</v>
       </c>
       <c r="J172" t="n">
-        <v>18.0522</v>
+        <v>17.3124</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1713</v>
+        <v>0.177</v>
       </c>
       <c r="J173" t="n">
-        <v>4.6251</v>
+        <v>4.779</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0061</v>
+        <v>0.0043</v>
       </c>
       <c r="J174" t="n">
-        <v>0.1647</v>
+        <v>0.1161</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.74</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2933</v>
+        <v>-0.3067</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.9191</v>
+        <v>-8.280900000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3505</v>
+        <v>-0.3624</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.4635</v>
+        <v>-9.784800000000001</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.55</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2094</v>
+        <v>1.1762</v>
       </c>
       <c r="J177" t="n">
-        <v>32.6538</v>
+        <v>31.7574</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8442</v>
+        <v>0.7966</v>
       </c>
       <c r="J178" t="n">
-        <v>22.7934</v>
+        <v>21.5082</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2188</v>
+        <v>0.2314</v>
       </c>
       <c r="J179" t="n">
-        <v>5.9076</v>
+        <v>6.2478</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0514</v>
+        <v>0.0704</v>
       </c>
       <c r="J180" t="n">
-        <v>1.3878</v>
+        <v>1.9008</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.213</v>
+        <v>-0.2025</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.751</v>
+        <v>-5.4675</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.85</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1377</v>
+        <v>-0.1626</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.1671</v>
+        <v>-3.7398</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.82</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1713</v>
+        <v>-0.1956</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.9399</v>
+        <v>-4.4988</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.71</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2843</v>
+        <v>-0.3056</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.5389</v>
+        <v>-7.0288</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.51</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4684</v>
+        <v>-0.4813</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.7732</v>
+        <v>-11.0699</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.46</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5153</v>
+        <v>-0.5252</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.8519</v>
+        <v>-12.0796</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.66</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3135</v>
+        <v>1.2928</v>
       </c>
       <c r="J187" t="n">
-        <v>30.2105</v>
+        <v>29.7344</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.37</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9215</v>
+        <v>0.871</v>
       </c>
       <c r="J188" t="n">
-        <v>21.1945</v>
+        <v>20.033</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.2</v>
       </c>
       <c r="I189" t="n">
-        <v>0.539</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J189" t="n">
-        <v>12.397</v>
+        <v>12.2061</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.539</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>12.397</v>
+        <v>12.2061</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.13</v>
       </c>
       <c r="I191" t="n">
-        <v>0.3592</v>
+        <v>0.3681</v>
       </c>
       <c r="J191" t="n">
-        <v>8.2616</v>
+        <v>8.4663</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6713</v>
+        <v>0.6432</v>
       </c>
       <c r="J192" t="n">
-        <v>19.4677</v>
+        <v>18.6528</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.97</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0467</v>
+        <v>-0.0557</v>
       </c>
       <c r="J193" t="n">
-        <v>-1.3543</v>
+        <v>-1.6153</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0467</v>
+        <v>-0.0557</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.3543</v>
+        <v>-1.6153</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.82</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2134</v>
+        <v>-0.2281</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.1886</v>
+        <v>-6.6149</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3404</v>
+        <v>-0.3527</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.871600000000001</v>
+        <v>-10.2283</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8423</v>
+        <v>0.7911</v>
       </c>
       <c r="J197" t="n">
-        <v>24.4267</v>
+        <v>22.9419</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5517</v>
+        <v>0.5341</v>
       </c>
       <c r="J198" t="n">
-        <v>15.9993</v>
+        <v>15.4889</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.15</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4504</v>
+        <v>0.4426</v>
       </c>
       <c r="J199" t="n">
-        <v>13.0616</v>
+        <v>12.8354</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.02</v>
       </c>
       <c r="I200" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0814</v>
       </c>
       <c r="J200" t="n">
-        <v>1.9459</v>
+        <v>2.3606</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2624</v>
+        <v>-0.2536</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.6096</v>
+        <v>-7.3544</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.611</v>
       </c>
       <c r="J202" t="n">
-        <v>16.1925</v>
+        <v>15.275</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3079</v>
+        <v>0.2975</v>
       </c>
       <c r="J203" t="n">
-        <v>7.6975</v>
+        <v>7.4375</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2666</v>
+        <v>-0.284</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.665</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.57</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4365</v>
+        <v>-0.4475</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.9125</v>
+        <v>-11.1875</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.45</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5467</v>
+        <v>-0.5512</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.6675</v>
+        <v>-13.78</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.62</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2828</v>
+        <v>1.257</v>
       </c>
       <c r="J207" t="n">
-        <v>32.07</v>
+        <v>31.425</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0689</v>
+        <v>1.0248</v>
       </c>
       <c r="J208" t="n">
-        <v>26.7225</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.24</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6476</v>
+        <v>0.6252</v>
       </c>
       <c r="J209" t="n">
-        <v>16.19</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.11</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3216</v>
+        <v>0.3299</v>
       </c>
       <c r="J210" t="n">
-        <v>8.039999999999999</v>
+        <v>8.2475</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.77</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7603</v>
+        <v>-0.6993</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.0075</v>
+        <v>-17.4825</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.521</v>
+        <v>0.5111</v>
       </c>
       <c r="J212" t="n">
-        <v>25.008</v>
+        <v>24.5328</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.18</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3946</v>
+        <v>0.3941</v>
       </c>
       <c r="J213" t="n">
-        <v>18.9408</v>
+        <v>18.9168</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0906</v>
+        <v>-0.1009</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.3488</v>
+        <v>-4.8432</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0906</v>
+        <v>-0.1009</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.3488</v>
+        <v>-4.8432</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2317</v>
+        <v>-0.2446</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.1216</v>
+        <v>-11.7408</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.24</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7108</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J217" t="n">
-        <v>34.1184</v>
+        <v>32.1072</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0051</v>
+        <v>-0.0035</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.2448</v>
+        <v>-0.168</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.99</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0594</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.8512</v>
+        <v>-3.0144</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1715</v>
+        <v>-0.1737</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.231999999999999</v>
+        <v>-8.3376</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2046</v>
+        <v>-0.2054</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.8208</v>
+        <v>-9.8592</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.47</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9438</v>
+        <v>0.8861</v>
       </c>
       <c r="J222" t="n">
-        <v>23.595</v>
+        <v>22.1525</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0568</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.42</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.126</v>
+        <v>-0.1406</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.15</v>
+        <v>-3.515</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3365</v>
+        <v>-0.3496</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.4125</v>
+        <v>-8.74</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.59</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4298</v>
+        <v>-0.4392</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.745</v>
+        <v>-10.98</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.33</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8794</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="J227" t="n">
-        <v>21.985</v>
+        <v>20.6275</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.21</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5737</v>
       </c>
       <c r="J228" t="n">
-        <v>14.8575</v>
+        <v>14.3425</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.11</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3419</v>
+        <v>0.3439</v>
       </c>
       <c r="J229" t="n">
-        <v>8.547499999999999</v>
+        <v>8.5975</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.06</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1968</v>
+        <v>0.2085</v>
       </c>
       <c r="J230" t="n">
-        <v>4.92</v>
+        <v>5.2125</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.03</v>
       </c>
       <c r="I231" t="n">
-        <v>0.0975</v>
+        <v>0.1132</v>
       </c>
       <c r="J231" t="n">
-        <v>2.4375</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.18</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4214</v>
+        <v>0.4138</v>
       </c>
       <c r="J232" t="n">
-        <v>11.3778</v>
+        <v>11.1726</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.14</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3439</v>
+        <v>0.3413</v>
       </c>
       <c r="J233" t="n">
-        <v>9.285299999999999</v>
+        <v>9.2151</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.9</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.128</v>
+        <v>-0.1421</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.456</v>
+        <v>-3.8367</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.82</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2119</v>
+        <v>-0.227</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.7213</v>
+        <v>-6.129</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.67</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3578</v>
+        <v>-0.3698</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.660600000000001</v>
+        <v>-9.9846</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.34</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9023</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="J237" t="n">
-        <v>24.3621</v>
+        <v>22.8231</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8794</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="J238" t="n">
-        <v>23.7438</v>
+        <v>22.2777</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.23</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6429</v>
+        <v>0.617</v>
       </c>
       <c r="J239" t="n">
-        <v>17.3583</v>
+        <v>16.659</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.21</v>
       </c>
       <c r="I240" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5737</v>
       </c>
       <c r="J240" t="n">
-        <v>16.0461</v>
+        <v>15.4899</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.63</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.0804</v>
+        <v>-0.9819</v>
       </c>
       <c r="J241" t="n">
-        <v>-29.1708</v>
+        <v>-26.5113</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.22</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4707</v>
+        <v>0.4642</v>
       </c>
       <c r="J242" t="n">
-        <v>14.121</v>
+        <v>13.926</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.18</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3975</v>
+        <v>0.3962</v>
       </c>
       <c r="J243" t="n">
-        <v>11.925</v>
+        <v>11.886</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.03</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0896</v>
+        <v>0.0984</v>
       </c>
       <c r="J244" t="n">
-        <v>2.688</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0896</v>
+        <v>-0.1001</v>
       </c>
       <c r="J245" t="n">
-        <v>-2.688</v>
+        <v>-3.003</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.7</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3378</v>
+        <v>-0.3489</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.134</v>
+        <v>-10.467</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.42</v>
       </c>
       <c r="I247" t="n">
-        <v>1.077</v>
+        <v>1.0241</v>
       </c>
       <c r="J247" t="n">
-        <v>32.31</v>
+        <v>30.723</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.11</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3602</v>
+        <v>0.3563</v>
       </c>
       <c r="J248" t="n">
-        <v>10.806</v>
+        <v>10.689</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0112</v>
+        <v>-0.0076</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.336</v>
+        <v>-0.228</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2749</v>
+        <v>-0.2699</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.247</v>
+        <v>-8.097</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6109</v>
+        <v>-0.5754</v>
       </c>
       <c r="J251" t="n">
-        <v>-18.327</v>
+        <v>-17.262</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4411/event_4411_evp_summary.xlsx
+++ b/database/event/4411/event_4411_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.533200000000001</v>
+        <v>8.6348</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4006</v>
+        <v>2.4292</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2603</v>
+        <v>3.3278</v>
       </c>
       <c r="E2" t="n">
-        <v>8.533200000000001</v>
+        <v>8.6348</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0207</v>
+        <v>2.9622</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5124</v>
+        <v>5.6726</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0723</v>
+        <v>4.6786</v>
       </c>
       <c r="I2" t="n">
-        <v>2.739</v>
+        <v>2.6269</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5124</v>
+        <v>5.6833</v>
       </c>
       <c r="K2" t="n">
         <v>157</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>8.2514</v>
+        <v>8.3102</v>
       </c>
       <c r="N2" t="n">
         <v>259</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8041</v>
+        <v>5.7292</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6328</v>
+        <v>1.6118</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0179</v>
+        <v>2.0041</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8041</v>
+        <v>5.7292</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7829</v>
+        <v>2.7745</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0212</v>
+        <v>2.9547</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2877</v>
+        <v>3.9742</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3153</v>
+        <v>2.2314</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0212</v>
+        <v>2.9547</v>
       </c>
       <c r="K3" t="n">
         <v>157</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3365</v>
+        <v>5.1861</v>
       </c>
       <c r="N3" t="n">
         <v>259</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9516</v>
+        <v>5.0432</v>
       </c>
       <c r="C4" t="n">
-        <v>1.393</v>
+        <v>1.4188</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6299</v>
+        <v>1.6916</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9516</v>
+        <v>5.0432</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4043</v>
+        <v>2.4546</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5473</v>
+        <v>2.5886</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0384</v>
+        <v>2.7729</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6407</v>
+        <v>1.5569</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5473</v>
+        <v>2.5886</v>
       </c>
       <c r="K4" t="n">
         <v>157</v>
@@ -621,7 +621,7 @@
         <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>4.188</v>
+        <v>4.1455</v>
       </c>
       <c r="N4" t="n">
         <v>259</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.61</v>
+        <v>3.5712</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0156</v>
+        <v>1.0047</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0191</v>
+        <v>1.0211</v>
       </c>
       <c r="E5" t="n">
-        <v>3.61</v>
+        <v>3.5712</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8902</v>
+        <v>2.9083</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7198</v>
+        <v>0.6629</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6417</v>
+        <v>4.4765</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5065</v>
+        <v>2.5134</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7198</v>
+        <v>0.6629</v>
       </c>
       <c r="K5" t="n">
         <v>127</v>
@@ -667,7 +667,7 @@
         <v>69</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2263</v>
+        <v>3.1763</v>
       </c>
       <c r="N5" t="n">
         <v>196</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5915</v>
+        <v>3.5705</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0104</v>
+        <v>1.0045</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0107</v>
+        <v>1.0207</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5915</v>
+        <v>3.5705</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8107</v>
+        <v>2.8106</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7808</v>
+        <v>0.7599</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3793</v>
+        <v>4.1098</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3648</v>
+        <v>2.3075</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7808</v>
+        <v>0.7599</v>
       </c>
       <c r="K6" t="n">
         <v>81</v>
@@ -713,7 +713,7 @@
         <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1456</v>
+        <v>3.0674</v>
       </c>
       <c r="N6" t="n">
         <v>138</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1867</v>
+        <v>3.0347</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8965</v>
+        <v>0.8537</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8264</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1867</v>
+        <v>3.0347</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1867</v>
+        <v>3.0347</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2498</v>
+        <v>4.0046</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2498</v>
+        <v>4.0046</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2498</v>
+        <v>4.0046</v>
       </c>
       <c r="N7" t="n">
         <v>156</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.032</v>
+        <v>2.8827</v>
       </c>
       <c r="C8" t="n">
-        <v>0.853</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.756</v>
+        <v>0.7074</v>
       </c>
       <c r="E8" t="n">
-        <v>3.032</v>
+        <v>2.8827</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0206</v>
+        <v>2.7746</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0114</v>
+        <v>0.1081</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0206</v>
+        <v>3.9746</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0911</v>
+        <v>2.2316</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0114</v>
+        <v>0.1081</v>
       </c>
       <c r="K8" t="n">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="L8" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1025</v>
+        <v>2.3397</v>
       </c>
       <c r="N8" t="n">
-        <v>196</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9148</v>
+        <v>2.7452</v>
       </c>
       <c r="C9" t="n">
-        <v>0.82</v>
+        <v>0.7723</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7027</v>
+        <v>0.6448</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9148</v>
+        <v>2.7452</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7701</v>
+        <v>1.8058</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1447</v>
+        <v>0.9394</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2454</v>
+        <v>1.8058</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2925</v>
+        <v>1.0139</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1447</v>
+        <v>0.9394</v>
       </c>
       <c r="K9" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="L9" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4372</v>
+        <v>1.9533</v>
       </c>
       <c r="N9" t="n">
-        <v>138</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6821</v>
+        <v>2.6535</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5967</v>
+        <v>0.603</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6821</v>
+        <v>2.6535</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7528</v>
+        <v>2.7509</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0707</v>
+        <v>-0.0974</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1882</v>
+        <v>3.8855</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2616</v>
+        <v>2.1816</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0707</v>
+        <v>-0.0974</v>
       </c>
       <c r="K10" t="n">
         <v>81</v>
@@ -897,7 +897,7 @@
         <v>57</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1909</v>
+        <v>2.0842</v>
       </c>
       <c r="N10" t="n">
         <v>138</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4303</v>
+        <v>2.4162</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6837</v>
+        <v>0.6797</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4821</v>
+        <v>0.4949</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4303</v>
+        <v>2.4162</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4303</v>
+        <v>2.4162</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5942</v>
+        <v>2.5871</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5942</v>
+        <v>2.5871</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5942</v>
+        <v>2.5871</v>
       </c>
       <c r="N11" t="n">
         <v>153</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3869</v>
+        <v>2.3338</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6715</v>
+        <v>0.6566</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4624</v>
+        <v>0.4574</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3869</v>
+        <v>2.3338</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3869</v>
+        <v>2.3338</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4992</v>
+        <v>2.3983</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4992</v>
+        <v>2.3983</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4992</v>
+        <v>2.3983</v>
       </c>
       <c r="N12" t="n">
         <v>156</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3068</v>
+        <v>2.2676</v>
       </c>
       <c r="C13" t="n">
-        <v>0.649</v>
+        <v>0.6379</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4259</v>
+        <v>0.4272</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3068</v>
+        <v>2.2676</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3068</v>
+        <v>1.9362</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.3314</v>
       </c>
       <c r="H13" t="n">
-        <v>2.324</v>
+        <v>1.9362</v>
       </c>
       <c r="I13" t="n">
-        <v>2.324</v>
+        <v>1.0871</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.3314</v>
       </c>
       <c r="K13" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M13" t="n">
-        <v>2.324</v>
+        <v>1.4185</v>
       </c>
       <c r="N13" t="n">
-        <v>153</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3041</v>
+        <v>2.2463</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6482</v>
+        <v>0.6319</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4247</v>
+        <v>0.4175</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3041</v>
+        <v>2.2463</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9876</v>
+        <v>2.2463</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3165</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9876</v>
+        <v>2.2463</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0733</v>
+        <v>2.2463</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3165</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L14" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3898</v>
+        <v>2.2463</v>
       </c>
       <c r="N14" t="n">
-        <v>281</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2567</v>
+        <v>2.2391</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6349</v>
+        <v>0.6299</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4031</v>
+        <v>0.4142</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2567</v>
+        <v>2.2391</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2567</v>
+        <v>2.5739</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.3348</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2567</v>
+        <v>3.2208</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2567</v>
+        <v>1.8084</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.3348</v>
       </c>
       <c r="K15" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2567</v>
+        <v>1.4736</v>
       </c>
       <c r="N15" t="n">
-        <v>156</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2203</v>
+        <v>2.2095</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6246</v>
+        <v>0.6216</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3865</v>
+        <v>0.4007</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2203</v>
+        <v>2.2095</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2172</v>
+        <v>2.2095</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0031</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4213</v>
+        <v>2.2095</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3075</v>
+        <v>2.2095</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0031</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L16" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3106</v>
+        <v>2.2095</v>
       </c>
       <c r="N16" t="n">
-        <v>259</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.183</v>
+        <v>2.1555</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6141</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3695</v>
+        <v>0.3761</v>
       </c>
       <c r="E17" t="n">
-        <v>2.183</v>
+        <v>2.1555</v>
       </c>
       <c r="F17" t="n">
-        <v>2.183</v>
+        <v>2.1555</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.183</v>
+        <v>2.1555</v>
       </c>
       <c r="I17" t="n">
-        <v>2.183</v>
+        <v>2.1555</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.183</v>
+        <v>2.1555</v>
       </c>
       <c r="N17" t="n">
         <v>156</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1119</v>
+        <v>2.0894</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5941</v>
+        <v>0.5878</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3372</v>
+        <v>0.346</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1119</v>
+        <v>2.0894</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4808</v>
+        <v>2.1463</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3689</v>
+        <v>-0.0569</v>
       </c>
       <c r="H18" t="n">
-        <v>3.291</v>
+        <v>2.1463</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7771</v>
+        <v>1.2051</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3689</v>
+        <v>-0.0569</v>
       </c>
       <c r="K18" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="L18" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4082</v>
+        <v>1.1482</v>
       </c>
       <c r="N18" t="n">
-        <v>196</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7494</v>
+        <v>1.5522</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4921</v>
+        <v>0.4367</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1722</v>
+        <v>0.1013</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7494</v>
+        <v>1.5522</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9043</v>
+        <v>1.6802</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1549</v>
+        <v>-0.128</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9043</v>
+        <v>1.6802</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0283</v>
+        <v>0.9434</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1549</v>
+        <v>-0.128</v>
       </c>
       <c r="K19" t="n">
         <v>81</v>
@@ -1311,7 +1311,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8734</v>
+        <v>0.8154</v>
       </c>
       <c r="N19" t="n">
         <v>138</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.529</v>
+        <v>1.4554</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4301</v>
+        <v>0.4094</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0718</v>
+        <v>0.0572</v>
       </c>
       <c r="E20" t="n">
-        <v>1.529</v>
+        <v>1.4554</v>
       </c>
       <c r="F20" t="n">
-        <v>1.529</v>
+        <v>1.4554</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.529</v>
+        <v>1.4554</v>
       </c>
       <c r="I20" t="n">
-        <v>1.529</v>
+        <v>1.4554</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.529</v>
+        <v>1.4554</v>
       </c>
       <c r="N20" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4386</v>
+        <v>1.3679</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4047</v>
+        <v>0.3848</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0307</v>
+        <v>0.0174</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4386</v>
+        <v>1.3679</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4386</v>
+        <v>1.3679</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4386</v>
+        <v>1.3679</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4386</v>
+        <v>1.3679</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4386</v>
+        <v>1.3679</v>
       </c>
       <c r="N21" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.8832</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2755</v>
+        <v>0.2485</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1784</v>
+        <v>-0.2034</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.8832</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8454</v>
+        <v>0.7728</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1339</v>
+        <v>0.1104</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8454</v>
+        <v>0.7728</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4565</v>
+        <v>0.4339</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1339</v>
+        <v>0.1104</v>
       </c>
       <c r="K22" t="n">
         <v>127</v>
@@ -1449,7 +1449,7 @@
         <v>69</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5904</v>
+        <v>0.5443</v>
       </c>
       <c r="N22" t="n">
         <v>196</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3254</v>
+        <v>0.3845</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0915</v>
+        <v>0.1082</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4761</v>
+        <v>-0.4306</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3254</v>
+        <v>0.3845</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.062</v>
+        <v>0.0436</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3874</v>
+        <v>0.3409</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.062</v>
+        <v>0.0436</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0335</v>
+        <v>0.0245</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3874</v>
+        <v>0.3409</v>
       </c>
       <c r="K23" t="n">
         <v>127</v>
@@ -1495,7 +1495,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3539</v>
+        <v>0.3654</v>
       </c>
       <c r="N23" t="n">
         <v>196</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2349</v>
+        <v>0.1472</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0414</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5173</v>
+        <v>-0.5387</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2349</v>
+        <v>0.1472</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2349</v>
+        <v>0.1472</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2349</v>
+        <v>0.1472</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2349</v>
+        <v>0.1472</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2349</v>
+        <v>0.1472</v>
       </c>
       <c r="N24" t="n">
         <v>123</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1924</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0541</v>
+        <v>0.0244</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5366</v>
+        <v>-0.5662</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1924</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1924</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1924</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1924</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1924</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>70</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0703</v>
+        <v>0.0504</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0198</v>
+        <v>0.0142</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.5828</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0703</v>
+        <v>0.0504</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0703</v>
+        <v>0.0504</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0703</v>
+        <v>0.0504</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0703</v>
+        <v>0.0504</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0703</v>
+        <v>0.0504</v>
       </c>
       <c r="N26" t="n">
         <v>156</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0273</v>
+        <v>0.0258</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0077</v>
+        <v>0.0073</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6118</v>
+        <v>-0.594</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0273</v>
+        <v>0.0258</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1181</v>
+        <v>0.1384</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.1126</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1181</v>
+        <v>0.1384</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0638</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.1126</v>
       </c>
       <c r="K27" t="n">
         <v>167</v>
@@ -1679,7 +1679,7 @@
         <v>114</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.02700000000000001</v>
+        <v>-0.0349</v>
       </c>
       <c r="N27" t="n">
         <v>281</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1198</v>
+        <v>-0.1705</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0337</v>
+        <v>-0.048</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6787</v>
+        <v>-0.6835</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1198</v>
+        <v>-0.1705</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1198</v>
+        <v>-0.1705</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1198</v>
+        <v>-0.1705</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1198</v>
+        <v>-0.1705</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1198</v>
+        <v>-0.1705</v>
       </c>
       <c r="N28" t="n">
         <v>123</v>
@@ -1734,323 +1734,323 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2861</v>
+        <v>-0.3462</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0805</v>
+        <v>-0.0974</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7544</v>
+        <v>-0.7635</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2861</v>
+        <v>-0.3462</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2574</v>
+        <v>-0.3462</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.5435</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2574</v>
+        <v>-0.3462</v>
       </c>
       <c r="I29" t="n">
-        <v>0.679</v>
+        <v>-0.3462</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.5435</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>167</v>
+        <v>70</v>
       </c>
       <c r="L29" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.8645</v>
+        <v>-0.3462</v>
       </c>
       <c r="N29" t="n">
-        <v>281</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3126</v>
+        <v>-0.5381</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.1514</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7665</v>
+        <v>-0.8509</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3126</v>
+        <v>-0.5381</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3126</v>
+        <v>-0.5381</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3126</v>
+        <v>-0.5381</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3126</v>
+        <v>-0.5381</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3126</v>
+        <v>-0.5381</v>
       </c>
       <c r="N30" t="n">
-        <v>70</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5483</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1513</v>
+        <v>-0.1542</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.869</v>
+        <v>-0.8556</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5483</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5377999999999999</v>
+        <v>0.9929</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-1.5412</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5377999999999999</v>
+        <v>0.9929</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5377999999999999</v>
+        <v>0.5575</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-1.5412</v>
       </c>
       <c r="K31" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.9836999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>153</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6592</v>
+        <v>-0.6482</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1854</v>
+        <v>-0.1824</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9243</v>
+        <v>-0.9011</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6592</v>
+        <v>-0.6482</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6592</v>
+        <v>-0.6482</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6592</v>
+        <v>-0.6482</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6592</v>
+        <v>-0.6482</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6592</v>
+        <v>-0.6482</v>
       </c>
       <c r="N32" t="n">
-        <v>123</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6987</v>
+        <v>-0.664</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1966</v>
+        <v>-0.1868</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9423</v>
+        <v>-0.9083</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6987</v>
+        <v>-0.664</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6987</v>
+        <v>-0.664</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6987</v>
+        <v>-0.664</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6987</v>
+        <v>-0.664</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6987</v>
+        <v>-0.664</v>
       </c>
       <c r="N33" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7005</v>
+        <v>-0.6684</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1971</v>
+        <v>-0.188</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9431</v>
+        <v>-0.9103</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7005</v>
+        <v>-0.6684</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7005</v>
+        <v>-0.6684</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7005</v>
+        <v>-0.6684</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7005</v>
+        <v>-0.6684</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7005</v>
+        <v>-0.6684</v>
       </c>
       <c r="N34" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7081</v>
+        <v>-0.752</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1992</v>
+        <v>-0.2116</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9465</v>
+        <v>-0.9484</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7081</v>
+        <v>-0.752</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7081</v>
+        <v>-0.752</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7081</v>
+        <v>-0.752</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7081</v>
+        <v>-0.752</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7081</v>
+        <v>-0.752</v>
       </c>
       <c r="N35" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1459</v>
+        <v>-1.1204</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3224</v>
+        <v>-0.3152</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1458</v>
+        <v>-1.1162</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1459</v>
+        <v>-1.1204</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1459</v>
+        <v>-1.1204</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1459</v>
+        <v>-1.1204</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1459</v>
+        <v>-1.1204</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1459</v>
+        <v>-1.1204</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3299</v>
+        <v>-1.309</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3741</v>
+        <v>-0.3683</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2296</v>
+        <v>-1.2021</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3299</v>
+        <v>-1.309</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3299</v>
+        <v>-1.309</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3299</v>
+        <v>-1.309</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3299</v>
+        <v>-1.309</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3299</v>
+        <v>-1.309</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.4948</v>
+        <v>-2.3022</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7018</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.7599</v>
+        <v>-1.6545</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.4948</v>
+        <v>-2.3022</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.2836</v>
+        <v>-2.1533</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2112</v>
+        <v>-0.1489</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.2836</v>
+        <v>-2.1533</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2331</v>
+        <v>-1.209</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2112</v>
+        <v>-0.1489</v>
       </c>
       <c r="K38" t="n">
         <v>167</v>
@@ -2185,7 +2185,7 @@
         <v>114</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4443</v>
+        <v>-1.3579</v>
       </c>
       <c r="N38" t="n">
         <v>281</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.5611</v>
+        <v>-2.4259</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7205</v>
+        <v>-0.6825</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.7901</v>
+        <v>-1.7109</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.5611</v>
+        <v>-2.4259</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.2226</v>
+        <v>-2.0958</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.3385</v>
+        <v>-0.3301</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.2226</v>
+        <v>-2.0958</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2002</v>
+        <v>-1.1767</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.3385</v>
+        <v>-0.3301</v>
       </c>
       <c r="K39" t="n">
         <v>157</v>
@@ -2231,7 +2231,7 @@
         <v>102</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5387</v>
+        <v>-1.5068</v>
       </c>
       <c r="N39" t="n">
         <v>259</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.0541</v>
+        <v>-2.8244</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8592</v>
+        <v>-0.7946</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.0145</v>
+        <v>-1.8924</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.0541</v>
+        <v>-2.8244</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3967</v>
+        <v>-1.196</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6574</v>
+        <v>-1.6284</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3967</v>
+        <v>-1.196</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7542</v>
+        <v>-0.6715</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.6574</v>
+        <v>-1.6284</v>
       </c>
       <c r="K40" t="n">
         <v>167</v>
@@ -2277,7 +2277,7 @@
         <v>114</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.4116</v>
+        <v>-2.2999</v>
       </c>
       <c r="N40" t="n">
         <v>281</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.9919</v>
+        <v>-3.6952</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.123</v>
+        <v>-1.0395</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.4414</v>
+        <v>-2.2891</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.9919</v>
+        <v>-3.6952</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.583</v>
+        <v>-3.3238</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4089</v>
+        <v>-0.3714</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.583</v>
+        <v>-3.3238</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9348</v>
+        <v>-1.8662</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4089</v>
+        <v>-0.3714</v>
       </c>
       <c r="K41" t="n">
         <v>81</v>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3437</v>
+        <v>-2.2376</v>
       </c>
       <c r="N41" t="n">
         <v>138</v>
@@ -2429,10 +2429,10 @@
         <v>1.03</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1323</v>
+        <v>0.1018</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3075</v>
+        <v>2.545</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.99</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0097</v>
+        <v>-0.0054</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2425</v>
+        <v>-0.135</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2376</v>
+        <v>-0.2189</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.94</v>
+        <v>-5.4725</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.75</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2856</v>
+        <v>-0.2675</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.14</v>
+        <v>-6.6875</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.65</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.378</v>
+        <v>-0.3647</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.1175</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.56</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2306</v>
+        <v>1.2496</v>
       </c>
       <c r="J7" t="n">
-        <v>30.765</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.45</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0296</v>
+        <v>1.0259</v>
       </c>
       <c r="J8" t="n">
-        <v>25.74</v>
+        <v>25.6475</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7423</v>
+        <v>0.7178</v>
       </c>
       <c r="J9" t="n">
-        <v>18.5575</v>
+        <v>17.945</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.27</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6561</v>
       </c>
       <c r="J10" t="n">
-        <v>17.075</v>
+        <v>16.4025</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.75</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7477</v>
+        <v>-0.7246</v>
       </c>
       <c r="J11" t="n">
-        <v>-18.6925</v>
+        <v>-18.115</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.8</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2016</v>
+        <v>-0.1848</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.032</v>
+        <v>-3.696</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2544</v>
+        <v>-0.2407</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.088</v>
+        <v>-4.814</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.57</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4198</v>
+        <v>-0.4123</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.396000000000001</v>
+        <v>-8.246</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.47</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5074</v>
+        <v>-0.5064</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.148</v>
+        <v>-10.128</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.44</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.676</v>
+        <v>-10.716</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>2.14</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J17" t="n">
-        <v>36.906</v>
+        <v>39.644</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.56</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1901</v>
+        <v>1.21</v>
       </c>
       <c r="J18" t="n">
-        <v>23.802</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7582</v>
+        <v>0.743</v>
       </c>
       <c r="J19" t="n">
-        <v>15.164</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.18</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4632</v>
+        <v>0.433</v>
       </c>
       <c r="J20" t="n">
-        <v>9.263999999999999</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.12</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3201</v>
+        <v>0.287</v>
       </c>
       <c r="J21" t="n">
-        <v>6.402</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8875</v>
+        <v>0.8505</v>
       </c>
       <c r="J22" t="n">
-        <v>30.175</v>
+        <v>28.917</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4201</v>
+        <v>0.3643</v>
       </c>
       <c r="J23" t="n">
-        <v>14.2834</v>
+        <v>12.3862</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1165</v>
+        <v>-0.098</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.961</v>
+        <v>-3.332</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.79</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2676</v>
+        <v>-0.2485</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.0984</v>
+        <v>-8.449</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2966</v>
+        <v>-0.279</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.0844</v>
+        <v>-9.486000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2582</v>
+        <v>1.2616</v>
       </c>
       <c r="J27" t="n">
-        <v>42.7788</v>
+        <v>42.8944</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6903</v>
+        <v>0.676</v>
       </c>
       <c r="J28" t="n">
-        <v>23.4702</v>
+        <v>22.984</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.27</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6296</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>21.4064</v>
+        <v>20.9916</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5975</v>
+        <v>-0.5614</v>
       </c>
       <c r="J30" t="n">
-        <v>-20.315</v>
+        <v>-19.0876</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7328</v>
+        <v>-0.7058</v>
       </c>
       <c r="J31" t="n">
-        <v>-24.9152</v>
+        <v>-23.9972</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.08</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2259</v>
+        <v>0.1816</v>
       </c>
       <c r="J32" t="n">
-        <v>5.1957</v>
+        <v>4.1768</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.98</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0384</v>
+        <v>-0.03</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8832</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.93</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1067</v>
+        <v>-0.0906</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.4541</v>
+        <v>-2.0838</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1413</v>
+        <v>-0.1229</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.2499</v>
+        <v>-2.8267</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2754</v>
+        <v>-0.2562</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.3342</v>
+        <v>-5.8926</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.74</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2605</v>
+        <v>1.2615</v>
       </c>
       <c r="J37" t="n">
-        <v>28.9915</v>
+        <v>29.0145</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.46</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8911</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>20.4953</v>
+        <v>20.1595</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.31</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6788</v>
+        <v>0.6673</v>
       </c>
       <c r="J39" t="n">
-        <v>15.6124</v>
+        <v>15.3479</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.91</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3627</v>
+        <v>-0.3233</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.3421</v>
+        <v>-7.4359</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.492</v>
+        <v>-0.4538</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.316</v>
+        <v>-10.4374</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5238</v>
+        <v>0.4927</v>
       </c>
       <c r="J42" t="n">
-        <v>14.1426</v>
+        <v>13.3029</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4225</v>
+        <v>0.3667</v>
       </c>
       <c r="J43" t="n">
-        <v>11.4075</v>
+        <v>9.9009</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1201</v>
+        <v>0.0919</v>
       </c>
       <c r="J44" t="n">
-        <v>3.2427</v>
+        <v>2.4813</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1027</v>
+        <v>-0.0853</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.7729</v>
+        <v>-2.3031</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.77</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2858</v>
+        <v>-0.2675</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.7166</v>
+        <v>-7.2225</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9497</v>
+        <v>0.9397</v>
       </c>
       <c r="J47" t="n">
-        <v>25.6419</v>
+        <v>25.3719</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.21</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5614</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>15.1578</v>
+        <v>14.8473</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.82</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5446</v>
+        <v>-0.5036</v>
       </c>
       <c r="J49" t="n">
-        <v>-14.7042</v>
+        <v>-13.5972</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.5279</v>
       </c>
       <c r="J50" t="n">
-        <v>-15.336</v>
+        <v>-14.2533</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.79</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6142</v>
+        <v>-0.5762</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.5834</v>
+        <v>-15.5574</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5997</v>
+        <v>0.571</v>
       </c>
       <c r="J52" t="n">
-        <v>25.1874</v>
+        <v>23.982</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.26</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4876</v>
+        <v>0.4467</v>
       </c>
       <c r="J53" t="n">
-        <v>20.4792</v>
+        <v>18.7614</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2366</v>
+        <v>0.1957</v>
       </c>
       <c r="J54" t="n">
-        <v>9.937200000000001</v>
+        <v>8.2194</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0351</v>
+        <v>-0.0258</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.4742</v>
+        <v>-1.0836</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.0673</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.4902</v>
+        <v>-2.8266</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.44</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9364</v>
+        <v>0.9285</v>
       </c>
       <c r="J57" t="n">
-        <v>39.3288</v>
+        <v>38.997</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.03</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1408</v>
+        <v>0.1114</v>
       </c>
       <c r="J58" t="n">
-        <v>5.9136</v>
+        <v>4.6788</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.83</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5111</v>
+        <v>-0.4694</v>
       </c>
       <c r="J59" t="n">
-        <v>-21.4662</v>
+        <v>-19.7148</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.82</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.4936</v>
       </c>
       <c r="J60" t="n">
-        <v>-22.4616</v>
+        <v>-20.7312</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7164</v>
+        <v>-0.6841</v>
       </c>
       <c r="J61" t="n">
-        <v>-30.0888</v>
+        <v>-28.7322</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.42</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9856</v>
+        <v>0.98</v>
       </c>
       <c r="J62" t="n">
-        <v>28.5824</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8968</v>
       </c>
       <c r="J63" t="n">
-        <v>26.4712</v>
+        <v>26.0072</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.31</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7743</v>
+        <v>0.7482</v>
       </c>
       <c r="J64" t="n">
-        <v>22.4547</v>
+        <v>21.6978</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.13</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3867</v>
+        <v>0.3523</v>
       </c>
       <c r="J65" t="n">
-        <v>11.2143</v>
+        <v>10.2167</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.73</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7799</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-22.6171</v>
+        <v>-21.9704</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.19</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4244</v>
+        <v>0.3674</v>
       </c>
       <c r="J67" t="n">
-        <v>12.3076</v>
+        <v>10.6546</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.96</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0704</v>
+        <v>-0.057</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.0416</v>
+        <v>-1.653</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.109</v>
+        <v>-0.0919</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.161</v>
+        <v>-2.6651</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1442</v>
+        <v>-0.125</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.1818</v>
+        <v>-3.625</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.188</v>
+        <v>-0.1676</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.452</v>
+        <v>-4.8604</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1265</v>
+        <v>1.1394</v>
       </c>
       <c r="J72" t="n">
-        <v>27.036</v>
+        <v>27.3456</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9479</v>
+        <v>0.9392</v>
       </c>
       <c r="J73" t="n">
-        <v>22.7496</v>
+        <v>22.5408</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.32</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7779</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>18.6696</v>
+        <v>18.1584</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.26</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6604</v>
+        <v>0.634</v>
       </c>
       <c r="J75" t="n">
-        <v>15.8496</v>
+        <v>15.216</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.95</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2532</v>
+        <v>-0.2184</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.0768</v>
+        <v>-5.2416</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.11</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2939</v>
+        <v>0.2443</v>
       </c>
       <c r="J77" t="n">
-        <v>7.0536</v>
+        <v>5.8632</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0895</v>
+        <v>0.0646</v>
       </c>
       <c r="J78" t="n">
-        <v>2.148</v>
+        <v>1.5504</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0586</v>
+        <v>0.0403</v>
       </c>
       <c r="J79" t="n">
-        <v>1.4064</v>
+        <v>0.9671999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0926</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.2224</v>
+        <v>-1.8792</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.44</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5661</v>
+        <v>-0.5764</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.5864</v>
+        <v>-13.8336</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.16</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3215</v>
+        <v>0.3157</v>
       </c>
       <c r="J82" t="n">
-        <v>9.002000000000001</v>
+        <v>8.839600000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1438</v>
+        <v>0.1287</v>
       </c>
       <c r="J83" t="n">
-        <v>4.0264</v>
+        <v>3.6036</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.86</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1781</v>
+        <v>-0.1606</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.9868</v>
+        <v>-4.4968</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.71</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3227</v>
+        <v>-0.306</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.035600000000001</v>
+        <v>-8.568</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.42</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5777</v>
+        <v>-0.5889</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.1756</v>
+        <v>-16.4892</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5915</v>
+        <v>0.5205</v>
       </c>
       <c r="J87" t="n">
-        <v>16.562</v>
+        <v>14.574</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.24</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3496</v>
+        <v>0.291</v>
       </c>
       <c r="J88" t="n">
-        <v>9.7888</v>
+        <v>8.148</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2901</v>
+        <v>0.2374</v>
       </c>
       <c r="J89" t="n">
-        <v>8.1228</v>
+        <v>6.6472</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0109</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.3052</v>
+        <v>-0.238</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1822</v>
+        <v>-0.1622</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.1016</v>
+        <v>-4.5416</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6091</v>
+        <v>0.5707</v>
       </c>
       <c r="J92" t="n">
-        <v>15.8366</v>
+        <v>14.8382</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.0078</v>
+        <v>-0.0026</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.6</v>
+        <v>-1.9968</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2312</v>
+        <v>-0.1943</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.0112</v>
+        <v>-5.0518</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.89</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.369</v>
+        <v>-0.3265</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.593999999999999</v>
+        <v>-8.489000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.49</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8855</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>23.023</v>
+        <v>21.8452</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2726</v>
+        <v>0.2242</v>
       </c>
       <c r="J98" t="n">
-        <v>7.0876</v>
+        <v>5.8292</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0738</v>
+        <v>0.0527</v>
       </c>
       <c r="J99" t="n">
-        <v>1.9188</v>
+        <v>1.3702</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.169</v>
+        <v>-0.1487</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.394</v>
+        <v>-3.8662</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.48</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5394</v>
+        <v>-0.5468</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.0244</v>
+        <v>-14.2168</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6006</v>
+        <v>0.5618</v>
       </c>
       <c r="J102" t="n">
-        <v>17.4174</v>
+        <v>16.2922</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.09</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3082</v>
+        <v>0.2685</v>
       </c>
       <c r="J103" t="n">
-        <v>8.937799999999999</v>
+        <v>7.7865</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1314</v>
+        <v>0.1055</v>
       </c>
       <c r="J104" t="n">
-        <v>3.8106</v>
+        <v>3.0595</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2364</v>
+        <v>-0.1986</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.8556</v>
+        <v>-5.7594</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.89</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3747</v>
+        <v>-0.3318</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.8663</v>
+        <v>-9.622199999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.4</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7338</v>
+        <v>0.677</v>
       </c>
       <c r="J107" t="n">
-        <v>21.2802</v>
+        <v>19.633</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6287</v>
+        <v>0.5692</v>
       </c>
       <c r="J108" t="n">
-        <v>18.2323</v>
+        <v>16.5068</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.92</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1285</v>
+        <v>-0.1094</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.7265</v>
+        <v>-3.1726</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.217</v>
+        <v>-0.1965</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.293</v>
+        <v>-5.6985</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2575</v>
+        <v>-0.2381</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.4675</v>
+        <v>-6.9049</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.82</v>
       </c>
       <c r="I112" t="n">
-        <v>1.4666</v>
+        <v>1.4957</v>
       </c>
       <c r="J112" t="n">
-        <v>29.332</v>
+        <v>29.914</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.6</v>
       </c>
       <c r="I113" t="n">
-        <v>1.195</v>
+        <v>1.2122</v>
       </c>
       <c r="J113" t="n">
-        <v>23.9</v>
+        <v>24.244</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.33</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7808</v>
+        <v>0.7664</v>
       </c>
       <c r="J114" t="n">
-        <v>15.616</v>
+        <v>15.328</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.3</v>
       </c>
       <c r="I115" t="n">
-        <v>0.7216</v>
+        <v>0.7035</v>
       </c>
       <c r="J115" t="n">
-        <v>14.432</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.16</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4202</v>
+        <v>0.3888</v>
       </c>
       <c r="J116" t="n">
-        <v>8.404</v>
+        <v>7.776</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.89</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1071</v>
+        <v>-0.0877</v>
       </c>
       <c r="J117" t="n">
-        <v>-2.142</v>
+        <v>-1.754</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.63</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3721</v>
+        <v>-0.3619</v>
       </c>
       <c r="J118" t="n">
-        <v>-7.442</v>
+        <v>-7.238</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.63</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3721</v>
+        <v>-0.3619</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.442</v>
+        <v>-7.238</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.54</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4505</v>
+        <v>-0.444</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.01</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.5</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4857</v>
+        <v>-0.4823</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.714</v>
+        <v>-9.646000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.34</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5212</v>
+        <v>0.5351</v>
       </c>
       <c r="J122" t="n">
-        <v>13.03</v>
+        <v>13.3775</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0592</v>
+        <v>0.0473</v>
       </c>
       <c r="J123" t="n">
-        <v>1.48</v>
+        <v>1.1825</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0571</v>
+        <v>-0.045</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.4275</v>
+        <v>-1.125</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1567</v>
+        <v>-0.1368</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.9175</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3552</v>
+        <v>-0.3409</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.880000000000001</v>
+        <v>-8.522500000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.27</v>
       </c>
       <c r="I127" t="n">
-        <v>0.386</v>
+        <v>0.3242</v>
       </c>
       <c r="J127" t="n">
-        <v>9.65</v>
+        <v>8.105</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3394</v>
+        <v>0.2814</v>
       </c>
       <c r="J128" t="n">
-        <v>8.484999999999999</v>
+        <v>7.035</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2541</v>
+        <v>0.2053</v>
       </c>
       <c r="J129" t="n">
-        <v>6.3525</v>
+        <v>5.1325</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0629</v>
+        <v>0.0451</v>
       </c>
       <c r="J130" t="n">
-        <v>1.5725</v>
+        <v>1.1275</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.01</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0202</v>
+        <v>0.0128</v>
       </c>
       <c r="J131" t="n">
-        <v>0.505</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.4</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9855</v>
+        <v>0.9806</v>
       </c>
       <c r="J132" t="n">
-        <v>29.565</v>
+        <v>29.418</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7353</v>
       </c>
       <c r="J133" t="n">
-        <v>22.938</v>
+        <v>22.059</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.03</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1267</v>
+        <v>0.1029</v>
       </c>
       <c r="J134" t="n">
-        <v>3.801</v>
+        <v>3.087</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0906</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J135" t="n">
-        <v>2.718</v>
+        <v>2.145</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.0297</v>
+        <v>-1.0315</v>
       </c>
       <c r="J136" t="n">
-        <v>-30.891</v>
+        <v>-30.945</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.43</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7856</v>
+        <v>0.7319</v>
       </c>
       <c r="J137" t="n">
-        <v>23.568</v>
+        <v>21.957</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.14</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3219</v>
+        <v>0.2702</v>
       </c>
       <c r="J138" t="n">
-        <v>9.657</v>
+        <v>8.106</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1263</v>
+        <v>-0.1074</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.789</v>
+        <v>-3.222</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.183</v>
+        <v>-0.1624</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.49</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.8</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2553</v>
+        <v>-0.2356</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.659</v>
+        <v>-7.068</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.9</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5473</v>
+        <v>1.5824</v>
       </c>
       <c r="J142" t="n">
-        <v>32.4933</v>
+        <v>33.2304</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.87</v>
       </c>
       <c r="I143" t="n">
-        <v>1.512</v>
+        <v>1.5447</v>
       </c>
       <c r="J143" t="n">
-        <v>31.752</v>
+        <v>32.4387</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.57</v>
       </c>
       <c r="I144" t="n">
-        <v>1.1486</v>
+        <v>1.1676</v>
       </c>
       <c r="J144" t="n">
-        <v>24.1206</v>
+        <v>24.5196</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.29</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6901</v>
+        <v>0.6714</v>
       </c>
       <c r="J145" t="n">
-        <v>14.4921</v>
+        <v>14.0994</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.99</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.143</v>
+        <v>-0.1291</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.003</v>
+        <v>-2.7111</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.82</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.17</v>
+        <v>-0.1495</v>
       </c>
       <c r="J147" t="n">
-        <v>-3.57</v>
+        <v>-3.1395</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.64</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3553</v>
+        <v>-0.3471</v>
       </c>
       <c r="J148" t="n">
-        <v>-7.4613</v>
+        <v>-7.2891</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.6</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3914</v>
+        <v>-0.3845</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.2194</v>
+        <v>-8.0745</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.49</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4852</v>
+        <v>-0.4824</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.1892</v>
+        <v>-10.1304</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.33</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6269</v>
+        <v>-0.6424</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.1649</v>
+        <v>-13.4904</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.66</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2901</v>
+        <v>1.3088</v>
       </c>
       <c r="J152" t="n">
-        <v>28.3822</v>
+        <v>28.7936</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.39</v>
       </c>
       <c r="I153" t="n">
-        <v>0.9065</v>
+        <v>0.8949</v>
       </c>
       <c r="J153" t="n">
-        <v>19.943</v>
+        <v>19.6878</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.36</v>
       </c>
       <c r="I154" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8349</v>
       </c>
       <c r="J154" t="n">
-        <v>18.7066</v>
+        <v>18.3678</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3903</v>
+        <v>0.3584</v>
       </c>
       <c r="J155" t="n">
-        <v>8.586600000000001</v>
+        <v>7.8848</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.08</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2359</v>
+        <v>0.2056</v>
       </c>
       <c r="J156" t="n">
-        <v>5.1898</v>
+        <v>4.5232</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4055</v>
+        <v>0.3742</v>
       </c>
       <c r="J157" t="n">
-        <v>8.920999999999999</v>
+        <v>8.2324</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.72</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2986</v>
+        <v>-0.2852</v>
       </c>
       <c r="J158" t="n">
-        <v>-6.5692</v>
+        <v>-6.2744</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.62</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3866</v>
+        <v>-0.3752</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.5052</v>
+        <v>-8.2544</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.52</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4749</v>
+        <v>-0.4703</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.4478</v>
+        <v>-10.3466</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.46</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5275</v>
+        <v>-0.5291</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.605</v>
+        <v>-11.6402</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4259</v>
+        <v>0.361</v>
       </c>
       <c r="J162" t="n">
-        <v>12.3511</v>
+        <v>10.469</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.29</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4145</v>
+        <v>0.3502</v>
       </c>
       <c r="J163" t="n">
-        <v>12.0205</v>
+        <v>10.1558</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.08</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1494</v>
+        <v>0.1147</v>
       </c>
       <c r="J164" t="n">
-        <v>4.3326</v>
+        <v>3.3263</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1072</v>
+        <v>-0.0893</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.1088</v>
+        <v>-2.5897</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.89</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1668</v>
+        <v>-0.1465</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.8372</v>
+        <v>-4.2485</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.29</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4628</v>
+        <v>0.4685</v>
       </c>
       <c r="J167" t="n">
-        <v>13.4212</v>
+        <v>13.5865</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0608</v>
+        <v>0.0485</v>
       </c>
       <c r="J168" t="n">
-        <v>1.7632</v>
+        <v>1.4065</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1773</v>
+        <v>-0.1571</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.1417</v>
+        <v>-4.5559</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.86</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.188</v>
+        <v>-0.1676</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.452</v>
+        <v>-4.8604</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2495</v>
+        <v>-0.2295</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.2355</v>
+        <v>-6.6555</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6412</v>
+        <v>0.5846</v>
       </c>
       <c r="J172" t="n">
-        <v>17.3124</v>
+        <v>15.7842</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.177</v>
+        <v>0.1383</v>
       </c>
       <c r="J173" t="n">
-        <v>4.779</v>
+        <v>3.7341</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0043</v>
+        <v>0.0023</v>
       </c>
       <c r="J174" t="n">
-        <v>0.1161</v>
+        <v>0.0621</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.74</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3067</v>
+        <v>-0.289</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.280900000000001</v>
+        <v>-7.803</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3624</v>
+        <v>-0.3484</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.784800000000001</v>
+        <v>-9.4068</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.55</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1762</v>
+        <v>1.1905</v>
       </c>
       <c r="J177" t="n">
-        <v>31.7574</v>
+        <v>32.1435</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7966</v>
+        <v>0.7714</v>
       </c>
       <c r="J178" t="n">
-        <v>21.5082</v>
+        <v>20.8278</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.07</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2314</v>
+        <v>0.2014</v>
       </c>
       <c r="J179" t="n">
-        <v>6.2478</v>
+        <v>5.4378</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0704</v>
+        <v>0.0542</v>
       </c>
       <c r="J180" t="n">
-        <v>1.9008</v>
+        <v>1.4634</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2025</v>
+        <v>-0.168</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.4675</v>
+        <v>-4.536</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.85</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1626</v>
+        <v>-0.1462</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.7398</v>
+        <v>-3.3626</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.82</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1956</v>
+        <v>-0.1801</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.4988</v>
+        <v>-4.1423</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.71</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3056</v>
+        <v>-0.2929</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.0288</v>
+        <v>-6.7367</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.51</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4813</v>
+        <v>-0.4774</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.0699</v>
+        <v>-10.9802</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.46</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5252</v>
+        <v>-0.5264</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.0796</v>
+        <v>-12.1072</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.66</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2928</v>
+        <v>1.3117</v>
       </c>
       <c r="J187" t="n">
-        <v>29.7344</v>
+        <v>30.1691</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.37</v>
       </c>
       <c r="I188" t="n">
-        <v>0.871</v>
+        <v>0.8562</v>
       </c>
       <c r="J188" t="n">
-        <v>20.033</v>
+        <v>19.6926</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.2</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="J189" t="n">
-        <v>12.2061</v>
+        <v>11.523</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="J190" t="n">
-        <v>12.2061</v>
+        <v>11.523</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.13</v>
       </c>
       <c r="I191" t="n">
-        <v>0.3681</v>
+        <v>0.3361</v>
       </c>
       <c r="J191" t="n">
-        <v>8.4663</v>
+        <v>7.7303</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6432</v>
+        <v>0.5869</v>
       </c>
       <c r="J192" t="n">
-        <v>18.6528</v>
+        <v>17.0201</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.97</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0557</v>
+        <v>-0.0444</v>
       </c>
       <c r="J193" t="n">
-        <v>-1.6153</v>
+        <v>-1.2876</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0557</v>
+        <v>-0.0444</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.6153</v>
+        <v>-1.2876</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.82</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2281</v>
+        <v>-0.2078</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.6149</v>
+        <v>-6.0262</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3527</v>
+        <v>-0.3379</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.2283</v>
+        <v>-9.799099999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7911</v>
+        <v>0.7641</v>
       </c>
       <c r="J197" t="n">
-        <v>22.9419</v>
+        <v>22.1589</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5341</v>
+        <v>0.4958</v>
       </c>
       <c r="J198" t="n">
-        <v>15.4889</v>
+        <v>14.3782</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.15</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4426</v>
+        <v>0.4039</v>
       </c>
       <c r="J199" t="n">
-        <v>12.8354</v>
+        <v>11.7131</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.02</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0814</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J200" t="n">
-        <v>2.3606</v>
+        <v>1.8618</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2536</v>
+        <v>-0.2147</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.3544</v>
+        <v>-6.2263</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.611</v>
+        <v>0.5633</v>
       </c>
       <c r="J202" t="n">
-        <v>15.275</v>
+        <v>14.0825</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2975</v>
+        <v>0.2511</v>
       </c>
       <c r="J203" t="n">
-        <v>7.4375</v>
+        <v>6.2775</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.284</v>
+        <v>-0.2661</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.1</v>
+        <v>-6.6525</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.57</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4475</v>
+        <v>-0.4406</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.1875</v>
+        <v>-11.015</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.45</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5512</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.78</v>
+        <v>-13.95</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.62</v>
       </c>
       <c r="I207" t="n">
-        <v>1.257</v>
+        <v>1.2744</v>
       </c>
       <c r="J207" t="n">
-        <v>31.425</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0248</v>
+        <v>1.0266</v>
       </c>
       <c r="J208" t="n">
-        <v>25.62</v>
+        <v>25.665</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.24</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6252</v>
+        <v>0.5948</v>
       </c>
       <c r="J209" t="n">
-        <v>15.63</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.11</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3299</v>
+        <v>0.2974</v>
       </c>
       <c r="J210" t="n">
-        <v>8.2475</v>
+        <v>7.435</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.77</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6993</v>
+        <v>-0.6715</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.4825</v>
+        <v>-16.7875</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.25</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5111</v>
+        <v>0.4518</v>
       </c>
       <c r="J212" t="n">
-        <v>24.5328</v>
+        <v>21.6864</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.18</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3941</v>
+        <v>0.3381</v>
       </c>
       <c r="J213" t="n">
-        <v>18.9168</v>
+        <v>16.2288</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1009</v>
+        <v>-0.0837</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.8432</v>
+        <v>-4.0176</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1009</v>
+        <v>-0.0837</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.8432</v>
+        <v>-4.0176</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2446</v>
+        <v>-0.2246</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.7408</v>
+        <v>-10.7808</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.24</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6335</v>
       </c>
       <c r="J217" t="n">
-        <v>32.1072</v>
+        <v>30.408</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0035</v>
+        <v>-0.0018</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.168</v>
+        <v>-0.0864</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.99</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.0452</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.0144</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1737</v>
+        <v>-0.1409</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.3376</v>
+        <v>-6.7632</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2054</v>
+        <v>-0.1698</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.8592</v>
+        <v>-8.150399999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.47</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8861</v>
+        <v>0.8471</v>
       </c>
       <c r="J222" t="n">
-        <v>22.1525</v>
+        <v>21.1775</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0555</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.69</v>
+        <v>-1.3875</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1406</v>
+        <v>-0.1225</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.515</v>
+        <v>-3.0625</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3496</v>
+        <v>-0.3344</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.74</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.59</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4392</v>
+        <v>-0.4323</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.98</v>
+        <v>-10.8075</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.33</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8011</v>
       </c>
       <c r="J227" t="n">
-        <v>20.6275</v>
+        <v>20.0275</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.21</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5737</v>
+        <v>0.5373</v>
       </c>
       <c r="J228" t="n">
-        <v>14.3425</v>
+        <v>13.4325</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.11</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3439</v>
+        <v>0.3085</v>
       </c>
       <c r="J229" t="n">
-        <v>8.5975</v>
+        <v>7.7125</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.06</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2085</v>
+        <v>0.1792</v>
       </c>
       <c r="J230" t="n">
-        <v>5.2125</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.03</v>
       </c>
       <c r="I231" t="n">
-        <v>0.1132</v>
+        <v>0.0921</v>
       </c>
       <c r="J231" t="n">
-        <v>2.83</v>
+        <v>2.3025</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.18</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4138</v>
+        <v>0.3576</v>
       </c>
       <c r="J232" t="n">
-        <v>11.1726</v>
+        <v>9.655200000000001</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.14</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3413</v>
+        <v>0.2881</v>
       </c>
       <c r="J233" t="n">
-        <v>9.2151</v>
+        <v>7.7787</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.9</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1421</v>
+        <v>-0.1235</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.8367</v>
+        <v>-3.3345</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.82</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.227</v>
+        <v>-0.2068</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.129</v>
+        <v>-5.5836</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.67</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3698</v>
+        <v>-0.3563</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.9846</v>
+        <v>-9.620100000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.34</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8227</v>
       </c>
       <c r="J237" t="n">
-        <v>22.8231</v>
+        <v>22.2129</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8011</v>
       </c>
       <c r="J238" t="n">
-        <v>22.2777</v>
+        <v>21.6297</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.23</v>
       </c>
       <c r="I239" t="n">
-        <v>0.617</v>
+        <v>0.5818</v>
       </c>
       <c r="J239" t="n">
-        <v>16.659</v>
+        <v>15.7086</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.21</v>
       </c>
       <c r="I240" t="n">
-        <v>0.5737</v>
+        <v>0.5373</v>
       </c>
       <c r="J240" t="n">
-        <v>15.4899</v>
+        <v>14.5071</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.63</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.9819</v>
+        <v>-0.98</v>
       </c>
       <c r="J241" t="n">
-        <v>-26.5113</v>
+        <v>-26.46</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.22</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4642</v>
+        <v>0.4057</v>
       </c>
       <c r="J242" t="n">
-        <v>13.926</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.18</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3962</v>
+        <v>0.3401</v>
       </c>
       <c r="J243" t="n">
-        <v>11.886</v>
+        <v>10.203</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.03</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0984</v>
+        <v>0.073</v>
       </c>
       <c r="J244" t="n">
-        <v>2.952</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1001</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J245" t="n">
-        <v>-3.003</v>
+        <v>-2.493</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.7</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3489</v>
+        <v>-0.3343</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.467</v>
+        <v>-10.029</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.42</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0241</v>
+        <v>1.0271</v>
       </c>
       <c r="J247" t="n">
-        <v>30.723</v>
+        <v>30.813</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.11</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3563</v>
+        <v>0.3158</v>
       </c>
       <c r="J248" t="n">
-        <v>10.689</v>
+        <v>9.474</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0076</v>
+        <v>-0.0046</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.228</v>
+        <v>-0.138</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2699</v>
+        <v>-0.23</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.097</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5754</v>
+        <v>-0.5359</v>
       </c>
       <c r="J251" t="n">
-        <v>-17.262</v>
+        <v>-16.077</v>
       </c>
     </row>
   </sheetData>
